--- a/xlsx/Hob.xlsx
+++ b/xlsx/Hob.xlsx
@@ -49131,7 +49131,7 @@
         <v>2803</v>
       </c>
     </row>
-    <row r="1132" s="2" customFormat="1" spans="1:12">
+    <row r="1132" s="2" customFormat="1" ht="138.85" spans="1:12">
       <c r="A1132" s="6">
         <v>20</v>
       </c>
@@ -49155,7 +49155,7 @@
         <v>1110</v>
       </c>
       <c r="I1132" s="6"/>
-      <c r="J1132" s="7" t="s">
+      <c r="J1132" s="14" t="s">
         <v>2790</v>
       </c>
       <c r="K1132" s="8" t="s">

--- a/xlsx/Hob.xlsx
+++ b/xlsx/Hob.xlsx
@@ -46339,7 +46339,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="K2:K314 D1:K1" emptyCellReference="1"/>
+    <ignoredError sqref="D1:K1 K2:K314" emptyCellReference="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/xlsx/Hob.xlsx
+++ b/xlsx/Hob.xlsx
@@ -9725,7 +9725,7 @@
     <t>op. 31</t>
   </si>
   <si>
-    <t>Sept Paroles du Christ en Croix, Version for String Quartet</t>
+    <t>Die sieben letzten Worte unseres Erlösers am Kreuze, version for string quartet</t>
   </si>
   <si>
     <t>Strings (2 Violins, Viola, Cello)</t>
@@ -9783,7 +9783,7 @@
     <t>Hob. XX:4</t>
   </si>
   <si>
-    <t>Die sieben letzten Worte unseres Erlösers am Kreuze, version for choir &amp; orchestra</t>
+    <t>Die sieben letzten Worte unseres Erlösers am Kreuze, version for choir and orchestra</t>
   </si>
   <si>
     <t>0. Introduction: Maestoso ed Adagio (D minor)
@@ -12764,7 +12764,7 @@
     <col min="1" max="1" width="11.6576576576577" style="4" customWidth="1"/>
     <col min="2" max="2" width="15.8288288288288" style="5" customWidth="1"/>
     <col min="3" max="4" width="11.6576576576577" style="4" customWidth="1"/>
-    <col min="5" max="5" width="35.4414414414414" style="5" customWidth="1"/>
+    <col min="5" max="5" width="82.2342342342342" style="5" customWidth="1"/>
     <col min="6" max="7" width="11.6576576576577" style="4" customWidth="1"/>
     <col min="8" max="10" width="23.7027027027027" style="5" customWidth="1"/>
     <col min="11" max="16382" width="8.48648648648649" style="3" customWidth="1"/>

--- a/xlsx/Hob.xlsx
+++ b/xlsx/Hob.xlsx
@@ -9,14 +9,14 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21942" windowHeight="9600"/>
+    <workbookView windowWidth="10971" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Hob. " sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hob. '!$A$1:$J$1331</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hob. '!$A$1:$J$1495</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8290" uniqueCount="3251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8644" uniqueCount="3560">
   <si>
     <t>SORT</t>
   </si>
@@ -10712,6 +10712,933 @@
   </si>
   <si>
     <t>Hob. XXIIb:Es3</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:1</t>
+  </si>
+  <si>
+    <t>Motette "Non nobis Domine"</t>
+  </si>
+  <si>
+    <t>Motet</t>
+  </si>
+  <si>
+    <t>verstimmigen Chor</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:2</t>
+  </si>
+  <si>
+    <t>Motette "Animae Deo gratae", bzw. "Agite Properate"</t>
+  </si>
+  <si>
+    <t>Soprano, verstimmigen gemischten Chor, 2 Violins, Basso, 2 Oboes, 2 Trumpets, Timpani, Organ</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:3</t>
+  </si>
+  <si>
+    <t>Hymne (Offertorium) "Ens aeternum attende votis", bzw. "Walte gnädig o ew'ge Liebe"</t>
+  </si>
+  <si>
+    <t>Offertory</t>
+  </si>
+  <si>
+    <t>verstimmigen gemischten Chor, 2 Violins, Basso, 2 Oboes, 2 Trumpets, Timpani, Organ</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:4</t>
+  </si>
+  <si>
+    <t>Motetto di Sancta Thecla "Quis stella radius"</t>
+  </si>
+  <si>
+    <t>Soprano, verstimmigen gemischten Chor, 2 Violins, Viola, Basso, Organ</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:5</t>
+  </si>
+  <si>
+    <t>Offertorium "Ad aras convolate"</t>
+  </si>
+  <si>
+    <t>verstimmigen gemischten Chor, 2 Violins, Viola, 2 Oboes, 2 Trombones, Organ</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:6</t>
+  </si>
+  <si>
+    <t>Motette "Salus et Gloria"</t>
+  </si>
+  <si>
+    <t>verstimmigen gemischten Chor, 2 Violins, 2 Trumpets, Timpani, Organ</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:7</t>
+  </si>
+  <si>
+    <t>Motetto de Tempore "Super flumina Babylonis"</t>
+  </si>
+  <si>
+    <t>Alto Solo, Soprano, Tenor, Basso ripieno, 2 Violins, Viola, 2 Trumpets, Timpani, Organ</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:8</t>
+  </si>
+  <si>
+    <t>Offertorium "Ardentes seraphini"</t>
+  </si>
+  <si>
+    <t>2 Sopranos, Alto, 2 Violins, Basso</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C1</t>
+  </si>
+  <si>
+    <t>Offertorium "O tremenda Majestas"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C2</t>
+  </si>
+  <si>
+    <t>Graduale "Coelestis urbs Jerusalem"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C3</t>
+  </si>
+  <si>
+    <t>Offertorium "Venite gentes"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C4</t>
+  </si>
+  <si>
+    <t>Offertorium "Exsultate Deo"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C5</t>
+  </si>
+  <si>
+    <t>Offertorium de Venerabili  "Sit laus plena"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C6</t>
+  </si>
+  <si>
+    <t>Motetto "Vidi cibitatem sanctam"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C7</t>
+  </si>
+  <si>
+    <t>Motette de Beate "Magna coeli Domina"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C8</t>
+  </si>
+  <si>
+    <t>Motette "Dulcis quies qua felix anima"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C9</t>
+  </si>
+  <si>
+    <t>Offertorium "Tanta in solemnitate"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C10</t>
+  </si>
+  <si>
+    <t>Motetto all' Offertorio "Laudate dominum"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C11</t>
+  </si>
+  <si>
+    <t>Offertorium "Fons vivos et origo"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C12</t>
+  </si>
+  <si>
+    <t>Chorus "Latetur ecclesia"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C13</t>
+  </si>
+  <si>
+    <t>Motette "Florete flores quasi lilium"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C14</t>
+  </si>
+  <si>
+    <t>Offertorium "Eja cantate et jubilate"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:C15</t>
+  </si>
+  <si>
+    <t>Graduale "Tu es Deus"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:D1</t>
+  </si>
+  <si>
+    <t>Offertorium "Mane nobiscum domine"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:D2</t>
+  </si>
+  <si>
+    <t>Offertorium "Huc omnes volate, nobiscum exultate"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:D3</t>
+  </si>
+  <si>
+    <t>Motetto "Benedicta et venerabilis"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:D4</t>
+  </si>
+  <si>
+    <t>Offertorium "Pastores loquebantur"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:D5</t>
+  </si>
+  <si>
+    <t>Offertorium "Te Deum reges"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:d1</t>
+  </si>
+  <si>
+    <t>Graduale "Ubi sunt misericordiae"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:d2</t>
+  </si>
+  <si>
+    <t>Offertorium "Laudate Dominum"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:Es1</t>
+  </si>
+  <si>
+    <t>Offertorium "Non me ad te avertit amor"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:Es2</t>
+  </si>
+  <si>
+    <t>Offertorium "Quis sicut Dominus"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:Es3</t>
+  </si>
+  <si>
+    <t>Offertorium "Veni sancte Spiritus"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:Es4</t>
+  </si>
+  <si>
+    <t>Motetto "Inimici circumcederunt nos"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:Es5</t>
+  </si>
+  <si>
+    <t>Motetto "Alma Dei creatoris"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:Es6</t>
+  </si>
+  <si>
+    <t>Offertorium "Salve o verum speculum"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:Es7</t>
+  </si>
+  <si>
+    <t>Oratorium ad Sepulchrum Domini</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:Es8</t>
+  </si>
+  <si>
+    <t>Oratorium de Passione</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:F1</t>
+  </si>
+  <si>
+    <t>Offertorium "O sacrum convivium"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:F2</t>
+  </si>
+  <si>
+    <t>Motette "Ad festum gaudiorum"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:F3</t>
+  </si>
+  <si>
+    <t>Offertorium de Venerabili  "Caro cibus" - "A sumente"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:G1</t>
+  </si>
+  <si>
+    <t>Offertorium "Confitemini Domino"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:G2</t>
+  </si>
+  <si>
+    <t>Motette "Veni Sancte Spriritus"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:G3</t>
+  </si>
+  <si>
+    <t>Motetto "Te adoro latens Deus"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:G4</t>
+  </si>
+  <si>
+    <t>Motetto "Exaudi me tu Domine"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:G5</t>
+  </si>
+  <si>
+    <t>Motetto "Gregem tuum, Pastor bone"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:G6</t>
+  </si>
+  <si>
+    <t>Offertorium "Inveni David"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:G7</t>
+  </si>
+  <si>
+    <t>Offertorium "Christum Regens"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:G8</t>
+  </si>
+  <si>
+    <t>Offertorium "Exultate justi in Domino"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:G9</t>
+  </si>
+  <si>
+    <t>Motetto "O coelitum beati"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:A1</t>
+  </si>
+  <si>
+    <t>Offertorium "Parvulus filius"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:A2</t>
+  </si>
+  <si>
+    <t>Motette "Veni ad me"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:A3</t>
+  </si>
+  <si>
+    <t>Graduale "In deo speravit"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:A4</t>
+  </si>
+  <si>
+    <t>Graduale "Alleluja"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:A5</t>
+  </si>
+  <si>
+    <t>Offertorium "Ave Maris Stella"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:a1</t>
+  </si>
+  <si>
+    <t>Motetto "Ave Maria"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:B1</t>
+  </si>
+  <si>
+    <t>Offertorium "O sacramentum pietatis"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:B2</t>
+  </si>
+  <si>
+    <t>Graduale "Mirabilis Deus"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:B3</t>
+  </si>
+  <si>
+    <t>Graduale "Cum complerentur dies Pentecostes"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:B4</t>
+  </si>
+  <si>
+    <t>Graduale "Iste est"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIa:B5</t>
+  </si>
+  <si>
+    <t>Offertorium "Sub tuum praesidium"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:1</t>
+  </si>
+  <si>
+    <t>Salve Regina</t>
+  </si>
+  <si>
+    <t>S-solo, vierstimmigen gemischten Chor, 2 vl, basso, org</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:2</t>
+  </si>
+  <si>
+    <t>Salve Regina "Salve Organo solo"</t>
+  </si>
+  <si>
+    <t>s, alt, t, b, 2 vl, vla oblig, basso, konzertierende orgel</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:3</t>
+  </si>
+  <si>
+    <t>Ave Regina</t>
+  </si>
+  <si>
+    <t>s-solo, vier- bzw, 2stimmigen gemschten chor, 2 vl, org</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:4</t>
+  </si>
+  <si>
+    <t>Salve Regina in einem Satz</t>
+  </si>
+  <si>
+    <t>2stimmigen chor (s, alt, t), 2 vl, vla, basso, org</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:5</t>
+  </si>
+  <si>
+    <t>s und alt-solo, 2 vl, basso, org</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:6</t>
+  </si>
+  <si>
+    <t>Ave Regina. Andante</t>
+  </si>
+  <si>
+    <t>4stimmigen gemischt chor, 2 vl, basso, 2 trmp, timp, org</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:C1</t>
+  </si>
+  <si>
+    <t>Salve Regina. Andante</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:C2</t>
+  </si>
+  <si>
+    <t>Salve Regina. Allegro</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:C3</t>
+  </si>
+  <si>
+    <t>Regina coeli laetare. Allegro moderato</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:C4</t>
+  </si>
+  <si>
+    <t>Regina coeli laetare. Allegro</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:C5</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:C6</t>
+  </si>
+  <si>
+    <t>Salve Regina. Moderato</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:C7</t>
+  </si>
+  <si>
+    <t>Salve Regina. Allegro - Allegro molto</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:D1</t>
+  </si>
+  <si>
+    <t>Salve Regina. Adagio</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:D2</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:D3</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:D4</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:D5</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:D6</t>
+  </si>
+  <si>
+    <t>Regina coeli laetare</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:Es1</t>
+  </si>
+  <si>
+    <t>Regina coeli laetare, Duetto. Allegro molto</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:Es2</t>
+  </si>
+  <si>
+    <t>Regina coeli laetare, Duetto. Presto</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:Es3</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:Es4</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:Es5</t>
+  </si>
+  <si>
+    <t>Salve Regina. Tradissimo</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:Es6</t>
+  </si>
+  <si>
+    <t>Salve Regina. Andante moderato</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:Es7</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:Es8</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:E1</t>
+  </si>
+  <si>
+    <t>Alma redemptoris mater</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:F1</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:F2</t>
+  </si>
+  <si>
+    <t>Ave Regina à Basso Solo</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:B1</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:B2</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:B3</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIb:B4</t>
+  </si>
+  <si>
+    <t>Motette "Alma redemptoris Mater"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:1</t>
+  </si>
+  <si>
+    <t>Te Deum</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:2</t>
+  </si>
+  <si>
+    <t>(Großes) Te Deum</t>
+  </si>
+  <si>
+    <t>4stimmigen gemischt chor, 2 vl, vla, vlc, basso, fl, 2 ob, 2 fag, 2 cor, 3 trmp (3 poasaunen mit dem chor), timp, org</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:3</t>
+  </si>
+  <si>
+    <t>Alleluja</t>
+  </si>
+  <si>
+    <t>4stimmigen gemischt chor, 2 vl, basso, org</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:4</t>
+  </si>
+  <si>
+    <t>4 Responsoria de Venerabili</t>
+  </si>
+  <si>
+    <t>4 singstimmen, 2 vl, 2 cor, basso, org</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:5</t>
+  </si>
+  <si>
+    <t>4 "Hymne de Venerabili"</t>
+  </si>
+  <si>
+    <t>4 singstimmen, 2 vl, vla, 2 ob 2 trmp, basso, org</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:6</t>
+  </si>
+  <si>
+    <t>Aria de Venera "Lauda Sion"</t>
+  </si>
+  <si>
+    <t>alt-solo, 2 vl, 2 fl, vla, org</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C1</t>
+  </si>
+  <si>
+    <t>Te Deum. Allegro</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C2</t>
+  </si>
+  <si>
+    <t>Litaney. Andante</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C3</t>
+  </si>
+  <si>
+    <t>Litaney. Allegro moderato</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C4</t>
+  </si>
+  <si>
+    <t>Litaney. Adagio</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C5</t>
+  </si>
+  <si>
+    <t>Tantum ergo. Allegro moderato</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C6</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C7</t>
+  </si>
+  <si>
+    <t>Tantum ergo. Largo</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C8</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C9</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C10</t>
+  </si>
+  <si>
+    <t>Tantum ergo. Moderato</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C11</t>
+  </si>
+  <si>
+    <t>Tantum ergo. Andante</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C12</t>
+  </si>
+  <si>
+    <t>Tantum ergo. Allegro</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C13</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C14</t>
+  </si>
+  <si>
+    <t>Vesper "Dixit Dominus"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C15</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C16</t>
+  </si>
+  <si>
+    <t>Litaney. Moderato</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C17</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C18</t>
+  </si>
+  <si>
+    <t>Litaney. Allegro ma poco</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C19</t>
+  </si>
+  <si>
+    <t>Pastorella de Nocte</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C20</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C21</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C22</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:C23</t>
+  </si>
+  <si>
+    <t>Chor "Nichts ist edler"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:c1</t>
+  </si>
+  <si>
+    <t>Miserere</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:Des1</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:D1</t>
+  </si>
+  <si>
+    <t>Te Deum. Moderato</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:D2</t>
+  </si>
+  <si>
+    <t>Laudate pueri</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:D3</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:D4</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:D5</t>
+  </si>
+  <si>
+    <t>Veni Sancte Spriritus</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:D6</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:D7</t>
+  </si>
+  <si>
+    <t>Litaney. Andante quasi Adagio (dorisch?)</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:D8</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:D9</t>
+  </si>
+  <si>
+    <t>Lob und Dankmsik (Chor) "Mächtiger, Beschützer deiner Kinder"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:Es1</t>
+  </si>
+  <si>
+    <t>Tantum ergo</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:F1</t>
+  </si>
+  <si>
+    <t>Aria (für Chor) "Menschen, frohlocket"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:F2</t>
+  </si>
+  <si>
+    <t>Lied (für Männerchor) "O Sanctissima"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:F3</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:F4</t>
+  </si>
+  <si>
+    <t>Litaney. Allegro</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:G1</t>
+  </si>
+  <si>
+    <t>Te Deum "Großer Gott wir loben Dich"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:G2</t>
+  </si>
+  <si>
+    <t>Litaney. Allegro non molto</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:G3</t>
+  </si>
+  <si>
+    <t>Sequenz "Lauda Sion"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:G4</t>
+  </si>
+  <si>
+    <t>Hymnus "Ave maris stella"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:G5</t>
+  </si>
+  <si>
+    <t>Pange lingua</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:g1</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:B1</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:B2</t>
+  </si>
+  <si>
+    <t>Chor "O Salutaris Hostia"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:B3</t>
+  </si>
+  <si>
+    <t>Aria pastorella "Lauft ihr"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:B4</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:B5</t>
+  </si>
+  <si>
+    <t>Hob. XXIIIc:B6</t>
+  </si>
+  <si>
+    <t>Hob. XXIIId:1</t>
+  </si>
+  <si>
+    <t>Cantilena pro Adventu "Ein' Magd, ein' Dienerin"</t>
+  </si>
+  <si>
+    <t>s-solo, 2 vl, vla oblig, basso, 2 cor, org</t>
+  </si>
+  <si>
+    <t>Hob. XXIIId:2</t>
+  </si>
+  <si>
+    <t>Aria de Adventu "Mutter Gottes mir erlaube"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIId:3</t>
+  </si>
+  <si>
+    <t>Cantilena pro Adventu "Jesu Redemptor"</t>
+  </si>
+  <si>
+    <t>s, 2 vl, vla, 2 cor, basso, org</t>
+  </si>
+  <si>
+    <t>Hob. XXIIId:C1</t>
+  </si>
+  <si>
+    <t>Aria "Quisquis gaudet Deo suo"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIId:C2</t>
+  </si>
+  <si>
+    <t>Aria "O Maria"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIId:C3</t>
+  </si>
+  <si>
+    <t>Aria "Banda fidelis turba"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIId:D1</t>
+  </si>
+  <si>
+    <t>Aria "Huc ad templum"</t>
+  </si>
+  <si>
+    <t>Hob. XXIIId:D2</t>
+  </si>
+  <si>
+    <t>Aria "Cantate Domino"</t>
   </si>
   <si>
     <t>Hob. XXVIII:1</t>
@@ -12758,15 +13685,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J1331"/>
+  <dimension ref="A1:J1495"/>
   <sheetFormatPr defaultColWidth="8.48648648648649" defaultRowHeight="30" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="11.6576576576577" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.6576576576577" style="4" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="15.8288288288288" style="5" customWidth="1"/>
-    <col min="3" max="4" width="11.6576576576577" style="4" customWidth="1"/>
-    <col min="5" max="5" width="82.2342342342342" style="5" customWidth="1"/>
-    <col min="6" max="7" width="11.6576576576577" style="4" customWidth="1"/>
-    <col min="8" max="10" width="23.7027027027027" style="5" customWidth="1"/>
+    <col min="3" max="4" width="11.6576576576577" style="4" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="34.5945945945946" style="5" customWidth="1"/>
+    <col min="6" max="6" width="11.6576576576577" style="4" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6576576576577" style="4" customWidth="1"/>
+    <col min="8" max="8" width="23.7027027027027" style="5" hidden="1" customWidth="1"/>
+    <col min="9" max="10" width="23.7027027027027" style="5" customWidth="1"/>
     <col min="11" max="16382" width="8.48648648648649" style="3" customWidth="1"/>
     <col min="16383" max="16384" width="8.48648648648649" style="3"/>
   </cols>
@@ -47741,1115 +48670,3813 @@
     </row>
     <row r="1289" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1289" s="7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B1289" s="8" t="s">
         <v>2995</v>
       </c>
       <c r="C1289" s="7"/>
-      <c r="D1289" s="7">
-        <v>1762</v>
-      </c>
-      <c r="E1289" s="10" t="s">
+      <c r="D1289" s="7"/>
+      <c r="E1289" s="8" t="s">
         <v>2996</v>
       </c>
       <c r="F1289" s="7" t="s">
         <v>2997</v>
       </c>
       <c r="G1289" s="7"/>
-      <c r="H1289" s="10" t="s">
+      <c r="H1289" s="8"/>
+      <c r="I1289" s="8" t="s">
         <v>2998</v>
       </c>
-      <c r="I1289" s="10" t="s">
-        <v>2999</v>
-      </c>
-      <c r="J1289" s="8" t="s">
-        <v>3000</v>
-      </c>
+      <c r="J1289" s="8"/>
     </row>
     <row r="1290" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1290" s="7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B1290" s="8" t="s">
-        <v>3001</v>
+        <v>2999</v>
       </c>
       <c r="C1290" s="7"/>
-      <c r="D1290" s="7">
-        <v>1780</v>
-      </c>
-      <c r="E1290" s="10" t="s">
-        <v>3002</v>
+      <c r="D1290" s="7"/>
+      <c r="E1290" s="8" t="s">
+        <v>3000</v>
       </c>
       <c r="F1290" s="7" t="s">
         <v>2997</v>
       </c>
       <c r="G1290" s="7"/>
-      <c r="H1290" s="10" t="s">
-        <v>3003</v>
-      </c>
-      <c r="I1290" s="10" t="s">
-        <v>3004</v>
-      </c>
-      <c r="J1290" s="8" t="s">
-        <v>3005</v>
-      </c>
+      <c r="H1290" s="8"/>
+      <c r="I1290" s="8" t="s">
+        <v>3001</v>
+      </c>
+      <c r="J1290" s="8"/>
     </row>
     <row r="1291" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1291" s="7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B1291" s="8" t="s">
-        <v>3006</v>
+        <v>3002</v>
       </c>
       <c r="C1291" s="7"/>
-      <c r="D1291" s="7">
-        <v>1782</v>
-      </c>
-      <c r="E1291" s="10" t="s">
-        <v>3007</v>
+      <c r="D1291" s="7"/>
+      <c r="E1291" s="8" t="s">
+        <v>3003</v>
       </c>
       <c r="F1291" s="7" t="s">
-        <v>2997</v>
+        <v>3004</v>
       </c>
       <c r="G1291" s="7"/>
-      <c r="H1291" s="10" t="s">
-        <v>3008</v>
-      </c>
-      <c r="I1291" s="10" t="s">
-        <v>3009</v>
-      </c>
-      <c r="J1291" s="8" t="s">
-        <v>3010</v>
-      </c>
+      <c r="H1291" s="8"/>
+      <c r="I1291" s="8" t="s">
+        <v>3005</v>
+      </c>
+      <c r="J1291" s="8"/>
     </row>
     <row r="1292" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1292" s="7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B1292" s="8" t="s">
-        <v>3011</v>
+        <v>3006</v>
       </c>
       <c r="C1292" s="7"/>
-      <c r="D1292" s="7">
-        <v>1783</v>
-      </c>
-      <c r="E1292" s="10" t="s">
-        <v>3012</v>
+      <c r="D1292" s="7"/>
+      <c r="E1292" s="8" t="s">
+        <v>3007</v>
       </c>
       <c r="F1292" s="7" t="s">
         <v>2997</v>
       </c>
       <c r="G1292" s="7"/>
-      <c r="H1292" s="10" t="s">
-        <v>3013</v>
-      </c>
-      <c r="I1292" s="10" t="s">
-        <v>3014</v>
-      </c>
-      <c r="J1292" s="8" t="s">
-        <v>3015</v>
-      </c>
+      <c r="H1292" s="8"/>
+      <c r="I1292" s="8" t="s">
+        <v>3008</v>
+      </c>
+      <c r="J1292" s="8"/>
     </row>
     <row r="1293" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1293" s="7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B1293" s="8" t="s">
-        <v>3016</v>
+        <v>3009</v>
       </c>
       <c r="C1293" s="7"/>
-      <c r="D1293" s="7">
-        <v>1791</v>
-      </c>
-      <c r="E1293" s="10" t="s">
-        <v>3017</v>
+      <c r="D1293" s="7"/>
+      <c r="E1293" s="8" t="s">
+        <v>3010</v>
       </c>
       <c r="F1293" s="7" t="s">
-        <v>2997</v>
+        <v>3004</v>
       </c>
       <c r="G1293" s="7"/>
-      <c r="H1293" s="10" t="s">
-        <v>3018</v>
-      </c>
-      <c r="I1293" s="10" t="s">
-        <v>3019</v>
-      </c>
-      <c r="J1293" s="8" t="s">
-        <v>3020</v>
-      </c>
+      <c r="H1293" s="8"/>
+      <c r="I1293" s="8" t="s">
+        <v>3011</v>
+      </c>
+      <c r="J1293" s="8"/>
     </row>
     <row r="1294" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1294" s="7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B1294" s="8" t="s">
-        <v>3021</v>
+        <v>3012</v>
       </c>
       <c r="C1294" s="7"/>
-      <c r="D1294" s="7">
-        <v>1766</v>
-      </c>
-      <c r="E1294" s="10" t="s">
-        <v>3022</v>
+      <c r="D1294" s="7"/>
+      <c r="E1294" s="8" t="s">
+        <v>3013</v>
       </c>
       <c r="F1294" s="7" t="s">
         <v>2997</v>
       </c>
       <c r="G1294" s="7"/>
-      <c r="H1294" s="10" t="s">
-        <v>3023</v>
-      </c>
-      <c r="I1294" s="10" t="s">
-        <v>3024</v>
+      <c r="H1294" s="8"/>
+      <c r="I1294" s="8" t="s">
+        <v>3014</v>
       </c>
       <c r="J1294" s="8"/>
     </row>
     <row r="1295" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1295" s="7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B1295" s="8" t="s">
-        <v>3025</v>
+        <v>3015</v>
       </c>
       <c r="C1295" s="7"/>
-      <c r="D1295" s="7">
-        <v>1768</v>
-      </c>
-      <c r="E1295" s="10" t="s">
-        <v>3026</v>
+      <c r="D1295" s="7"/>
+      <c r="E1295" s="8" t="s">
+        <v>3016</v>
       </c>
       <c r="F1295" s="7" t="s">
         <v>2997</v>
       </c>
       <c r="G1295" s="7"/>
-      <c r="H1295" s="10" t="s">
-        <v>3003</v>
-      </c>
-      <c r="I1295" s="10" t="s">
-        <v>3027</v>
-      </c>
-      <c r="J1295" s="8" t="s">
-        <v>3028</v>
-      </c>
+      <c r="H1295" s="8"/>
+      <c r="I1295" s="8" t="s">
+        <v>3017</v>
+      </c>
+      <c r="J1295" s="8"/>
     </row>
     <row r="1296" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1296" s="7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B1296" s="8" t="s">
-        <v>3029</v>
+        <v>3018</v>
       </c>
       <c r="C1296" s="7"/>
-      <c r="D1296" s="7">
-        <v>1769</v>
-      </c>
-      <c r="E1296" s="10" t="s">
-        <v>3030</v>
+      <c r="D1296" s="7"/>
+      <c r="E1296" s="8" t="s">
+        <v>3019</v>
       </c>
       <c r="F1296" s="7" t="s">
-        <v>2997</v>
+        <v>3004</v>
       </c>
       <c r="G1296" s="7"/>
-      <c r="H1296" s="10" t="s">
-        <v>3003</v>
-      </c>
-      <c r="I1296" s="10" t="s">
-        <v>3031</v>
-      </c>
-      <c r="J1296" s="8" t="s">
-        <v>3028</v>
-      </c>
+      <c r="H1296" s="8"/>
+      <c r="I1296" s="8" t="s">
+        <v>3020</v>
+      </c>
+      <c r="J1296" s="8"/>
     </row>
     <row r="1297" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1297" s="7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B1297" s="8" t="s">
-        <v>3032</v>
+        <v>3021</v>
       </c>
       <c r="C1297" s="7"/>
-      <c r="D1297" s="7">
-        <v>1773</v>
-      </c>
-      <c r="E1297" s="10" t="s">
-        <v>3033</v>
-      </c>
-      <c r="F1297" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="D1297" s="7"/>
+      <c r="E1297" s="8" t="s">
+        <v>3022</v>
+      </c>
+      <c r="F1297" s="7"/>
       <c r="G1297" s="7"/>
-      <c r="H1297" s="10" t="s">
-        <v>3034</v>
-      </c>
-      <c r="I1297" s="10" t="s">
-        <v>3035</v>
-      </c>
-      <c r="J1297" s="8" t="s">
-        <v>3036</v>
-      </c>
+      <c r="H1297" s="8"/>
+      <c r="I1297" s="8"/>
+      <c r="J1297" s="8"/>
     </row>
     <row r="1298" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1298" s="7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B1298" s="8" t="s">
-        <v>3037</v>
+        <v>3023</v>
       </c>
       <c r="C1298" s="7"/>
-      <c r="D1298" s="7">
-        <v>1775</v>
-      </c>
-      <c r="E1298" s="10" t="s">
-        <v>3038</v>
-      </c>
-      <c r="F1298" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="D1298" s="7"/>
+      <c r="E1298" s="8" t="s">
+        <v>3024</v>
+      </c>
+      <c r="F1298" s="7"/>
       <c r="G1298" s="7"/>
-      <c r="H1298" s="10" t="s">
-        <v>3003</v>
-      </c>
-      <c r="I1298" s="10" t="s">
-        <v>3039</v>
-      </c>
-      <c r="J1298" s="8" t="s">
-        <v>3040</v>
-      </c>
+      <c r="H1298" s="8"/>
+      <c r="I1298" s="8"/>
+      <c r="J1298" s="8"/>
     </row>
     <row r="1299" s="3" customFormat="1" customHeight="1" spans="1:10">
       <c r="A1299" s="7">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B1299" s="8" t="s">
-        <v>3041</v>
+        <v>3025</v>
       </c>
       <c r="C1299" s="7"/>
-      <c r="D1299" s="7">
-        <v>1777</v>
-      </c>
-      <c r="E1299" s="10" t="s">
-        <v>3042</v>
-      </c>
-      <c r="F1299" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="D1299" s="7"/>
+      <c r="E1299" s="8" t="s">
+        <v>3026</v>
+      </c>
+      <c r="F1299" s="7"/>
       <c r="G1299" s="7"/>
-      <c r="H1299" s="10" t="s">
-        <v>3003</v>
-      </c>
-      <c r="I1299" s="10" t="s">
-        <v>3043</v>
-      </c>
-      <c r="J1299" s="8" t="s">
-        <v>3044</v>
-      </c>
+      <c r="H1299" s="8"/>
+      <c r="I1299" s="8"/>
+      <c r="J1299" s="8"/>
     </row>
     <row r="1300" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1300" s="7">
-        <v>28</v>
-      </c>
+      <c r="A1300" s="7"/>
       <c r="B1300" s="8" t="s">
-        <v>3045</v>
+        <v>3027</v>
       </c>
       <c r="C1300" s="7"/>
-      <c r="D1300" s="7" t="s">
-        <v>3046</v>
-      </c>
-      <c r="E1300" s="10" t="s">
-        <v>3047</v>
-      </c>
-      <c r="F1300" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="D1300" s="7"/>
+      <c r="E1300" s="8" t="s">
+        <v>3028</v>
+      </c>
+      <c r="F1300" s="7"/>
       <c r="G1300" s="7"/>
-      <c r="H1300" s="10" t="s">
-        <v>3003</v>
-      </c>
-      <c r="I1300" s="10" t="s">
-        <v>3048</v>
-      </c>
-      <c r="J1300" s="8" t="s">
-        <v>3049</v>
-      </c>
+      <c r="H1300" s="8"/>
+      <c r="I1300" s="8"/>
+      <c r="J1300" s="8"/>
     </row>
     <row r="1301" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1301" s="7">
-        <v>28</v>
-      </c>
+      <c r="A1301" s="7"/>
       <c r="B1301" s="8" t="s">
-        <v>3050</v>
+        <v>3029</v>
       </c>
       <c r="C1301" s="7"/>
-      <c r="D1301" s="7">
-        <v>1779</v>
-      </c>
-      <c r="E1301" s="10" t="s">
-        <v>3051</v>
-      </c>
-      <c r="F1301" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="D1301" s="7"/>
+      <c r="E1301" s="8" t="s">
+        <v>3030</v>
+      </c>
+      <c r="F1301" s="7"/>
       <c r="G1301" s="7"/>
-      <c r="H1301" s="10" t="s">
-        <v>3052</v>
-      </c>
-      <c r="I1301" s="10" t="s">
-        <v>3053</v>
-      </c>
-      <c r="J1301" s="8" t="s">
-        <v>3054</v>
-      </c>
+      <c r="H1301" s="8"/>
+      <c r="I1301" s="8"/>
+      <c r="J1301" s="8"/>
     </row>
     <row r="1302" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1302" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1302" s="7"/>
       <c r="B1302" s="8" t="s">
-        <v>3055</v>
+        <v>3031</v>
       </c>
       <c r="C1302" s="7"/>
-      <c r="D1302" s="7" t="s">
-        <v>3056</v>
-      </c>
+      <c r="D1302" s="7"/>
       <c r="E1302" s="8" t="s">
-        <v>3057</v>
-      </c>
-      <c r="F1302" s="7" t="s">
-        <v>3058</v>
-      </c>
+        <v>3032</v>
+      </c>
+      <c r="F1302" s="7"/>
       <c r="G1302" s="7"/>
-      <c r="H1302" s="8" t="s">
-        <v>3059</v>
-      </c>
-      <c r="I1302" s="8" t="s">
-        <v>3060</v>
-      </c>
-      <c r="J1302" s="10"/>
+      <c r="H1302" s="8"/>
+      <c r="I1302" s="8"/>
+      <c r="J1302" s="8"/>
     </row>
     <row r="1303" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1303" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1303" s="7"/>
       <c r="B1303" s="8" t="s">
-        <v>3061</v>
+        <v>3033</v>
       </c>
       <c r="C1303" s="7"/>
-      <c r="D1303" s="7" t="s">
-        <v>3062</v>
-      </c>
-      <c r="E1303" s="10" t="s">
-        <v>3063</v>
-      </c>
-      <c r="F1303" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="D1303" s="7"/>
+      <c r="E1303" s="8" t="s">
+        <v>3034</v>
+      </c>
+      <c r="F1303" s="7"/>
       <c r="G1303" s="7"/>
       <c r="H1303" s="8"/>
       <c r="I1303" s="8"/>
-      <c r="J1303" s="10" t="s">
-        <v>1881</v>
-      </c>
+      <c r="J1303" s="8"/>
     </row>
     <row r="1304" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1304" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1304" s="7"/>
       <c r="B1304" s="8" t="s">
-        <v>3064</v>
+        <v>3035</v>
       </c>
       <c r="C1304" s="7"/>
-      <c r="D1304" s="7">
-        <v>1768</v>
-      </c>
-      <c r="E1304" s="10" t="s">
-        <v>3065</v>
-      </c>
-      <c r="F1304" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="D1304" s="7"/>
+      <c r="E1304" s="8" t="s">
+        <v>3036</v>
+      </c>
+      <c r="F1304" s="7"/>
       <c r="G1304" s="7"/>
       <c r="H1304" s="8"/>
       <c r="I1304" s="8"/>
-      <c r="J1304" s="10" t="s">
-        <v>3066</v>
-      </c>
+      <c r="J1304" s="8"/>
     </row>
     <row r="1305" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1305" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1305" s="7"/>
       <c r="B1305" s="8" t="s">
-        <v>3067</v>
+        <v>3037</v>
       </c>
       <c r="C1305" s="7"/>
-      <c r="D1305" s="7">
-        <v>1783</v>
-      </c>
-      <c r="E1305" s="10" t="s">
-        <v>3068</v>
-      </c>
-      <c r="F1305" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="D1305" s="7"/>
+      <c r="E1305" s="8" t="s">
+        <v>3038</v>
+      </c>
+      <c r="F1305" s="7"/>
       <c r="G1305" s="7"/>
       <c r="H1305" s="8"/>
       <c r="I1305" s="8"/>
-      <c r="J1305" s="10" t="s">
-        <v>3069</v>
-      </c>
+      <c r="J1305" s="8"/>
     </row>
     <row r="1306" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1306" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1306" s="7"/>
       <c r="B1306" s="8" t="s">
-        <v>3070</v>
+        <v>3039</v>
       </c>
       <c r="C1306" s="7"/>
-      <c r="D1306" s="7" t="s">
-        <v>3071</v>
-      </c>
-      <c r="E1306" s="10" t="s">
-        <v>3072</v>
-      </c>
-      <c r="F1306" s="7" t="s">
-        <v>3058</v>
-      </c>
+      <c r="D1306" s="7"/>
+      <c r="E1306" s="8" t="s">
+        <v>3040</v>
+      </c>
+      <c r="F1306" s="7"/>
       <c r="G1306" s="7"/>
-      <c r="H1306" s="10" t="s">
-        <v>3073</v>
-      </c>
+      <c r="H1306" s="8"/>
       <c r="I1306" s="8"/>
-      <c r="J1306" s="10" t="s">
-        <v>1881</v>
-      </c>
+      <c r="J1306" s="8"/>
     </row>
     <row r="1307" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1307" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1307" s="7"/>
       <c r="B1307" s="8" t="s">
-        <v>3074</v>
+        <v>3041</v>
       </c>
       <c r="C1307" s="7"/>
-      <c r="D1307" s="7">
-        <v>1773</v>
-      </c>
-      <c r="E1307" s="10" t="s">
-        <v>3075</v>
-      </c>
-      <c r="F1307" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="D1307" s="7"/>
+      <c r="E1307" s="8" t="s">
+        <v>3042</v>
+      </c>
+      <c r="F1307" s="7"/>
       <c r="G1307" s="7"/>
       <c r="H1307" s="8"/>
-      <c r="I1307" s="10" t="s">
-        <v>3076</v>
-      </c>
-      <c r="J1307" s="10" t="s">
-        <v>3077</v>
-      </c>
+      <c r="I1307" s="8"/>
+      <c r="J1307" s="8"/>
     </row>
     <row r="1308" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1308" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1308" s="7"/>
       <c r="B1308" s="8" t="s">
-        <v>3078</v>
+        <v>3043</v>
       </c>
       <c r="C1308" s="7"/>
-      <c r="D1308" s="7">
-        <v>1773</v>
-      </c>
-      <c r="E1308" s="10" t="s">
-        <v>3079</v>
-      </c>
-      <c r="F1308" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="D1308" s="7"/>
+      <c r="E1308" s="8" t="s">
+        <v>3044</v>
+      </c>
+      <c r="F1308" s="7"/>
       <c r="G1308" s="7"/>
       <c r="H1308" s="8"/>
-      <c r="I1308" s="10" t="s">
-        <v>3080</v>
-      </c>
-      <c r="J1308" s="10" t="s">
-        <v>1881</v>
-      </c>
+      <c r="I1308" s="8"/>
+      <c r="J1308" s="8"/>
     </row>
     <row r="1309" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1309" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1309" s="7"/>
       <c r="B1309" s="8" t="s">
-        <v>3081</v>
+        <v>3045</v>
       </c>
       <c r="C1309" s="7"/>
-      <c r="D1309" s="7">
-        <v>1773</v>
-      </c>
-      <c r="E1309" s="10" t="s">
-        <v>3082</v>
-      </c>
-      <c r="F1309" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="D1309" s="7"/>
+      <c r="E1309" s="8" t="s">
+        <v>3046</v>
+      </c>
+      <c r="F1309" s="7"/>
       <c r="G1309" s="7"/>
       <c r="H1309" s="8"/>
-      <c r="I1309" s="10" t="s">
-        <v>3083</v>
-      </c>
-      <c r="J1309" s="10" t="s">
-        <v>1881</v>
-      </c>
+      <c r="I1309" s="8"/>
+      <c r="J1309" s="8"/>
     </row>
     <row r="1310" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1310" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1310" s="7"/>
       <c r="B1310" s="8" t="s">
-        <v>3084</v>
+        <v>3047</v>
       </c>
       <c r="C1310" s="7"/>
-      <c r="D1310" s="7">
-        <v>1776</v>
-      </c>
-      <c r="E1310" s="10" t="s">
-        <v>3085</v>
-      </c>
-      <c r="F1310" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="D1310" s="7"/>
+      <c r="E1310" s="8" t="s">
+        <v>3048</v>
+      </c>
+      <c r="F1310" s="7"/>
       <c r="G1310" s="7"/>
       <c r="H1310" s="8"/>
-      <c r="I1310" s="10" t="s">
-        <v>3086</v>
-      </c>
-      <c r="J1310" s="10" t="s">
-        <v>3087</v>
-      </c>
+      <c r="I1310" s="8"/>
+      <c r="J1310" s="8"/>
     </row>
     <row r="1311" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1311" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1311" s="7"/>
       <c r="B1311" s="8" t="s">
-        <v>3088</v>
+        <v>3049</v>
       </c>
       <c r="C1311" s="7"/>
       <c r="D1311" s="7"/>
-      <c r="E1311" s="10" t="s">
-        <v>3089</v>
-      </c>
-      <c r="F1311" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="E1311" s="8" t="s">
+        <v>3050</v>
+      </c>
+      <c r="F1311" s="7"/>
       <c r="G1311" s="7"/>
       <c r="H1311" s="8"/>
-      <c r="I1311" s="8" t="s">
-        <v>3090</v>
-      </c>
-      <c r="J1311" s="10" t="s">
-        <v>3091</v>
-      </c>
+      <c r="I1311" s="8"/>
+      <c r="J1311" s="8"/>
     </row>
     <row r="1312" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1312" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1312" s="7"/>
       <c r="B1312" s="8" t="s">
-        <v>3092</v>
+        <v>3051</v>
       </c>
       <c r="C1312" s="7"/>
-      <c r="D1312" s="7">
-        <v>1777</v>
-      </c>
-      <c r="E1312" s="10" t="s">
-        <v>3093</v>
-      </c>
-      <c r="F1312" s="7" t="s">
-        <v>2997</v>
-      </c>
+      <c r="D1312" s="7"/>
+      <c r="E1312" s="8" t="s">
+        <v>3052</v>
+      </c>
+      <c r="F1312" s="7"/>
       <c r="G1312" s="7"/>
       <c r="H1312" s="8"/>
       <c r="I1312" s="8"/>
-      <c r="J1312" s="10" t="s">
-        <v>3094</v>
-      </c>
+      <c r="J1312" s="8"/>
     </row>
     <row r="1313" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1313" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1313" s="7"/>
       <c r="B1313" s="8" t="s">
-        <v>3095</v>
+        <v>3053</v>
       </c>
       <c r="C1313" s="7"/>
-      <c r="D1313" s="7">
-        <v>1751</v>
-      </c>
-      <c r="E1313" s="10" t="s">
-        <v>3096</v>
-      </c>
-      <c r="F1313" s="7" t="s">
-        <v>3058</v>
-      </c>
+      <c r="D1313" s="7"/>
+      <c r="E1313" s="8" t="s">
+        <v>3054</v>
+      </c>
+      <c r="F1313" s="7"/>
       <c r="G1313" s="7"/>
       <c r="H1313" s="8"/>
       <c r="I1313" s="8"/>
-      <c r="J1313" s="10" t="s">
-        <v>3097</v>
-      </c>
+      <c r="J1313" s="8"/>
     </row>
     <row r="1314" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1314" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1314" s="7"/>
       <c r="B1314" s="8" t="s">
-        <v>3098</v>
+        <v>3055</v>
       </c>
       <c r="C1314" s="7"/>
-      <c r="D1314" s="7">
-        <v>1758</v>
-      </c>
-      <c r="E1314" s="10" t="s">
-        <v>3099</v>
-      </c>
-      <c r="F1314" s="7" t="s">
-        <v>3058</v>
-      </c>
+      <c r="D1314" s="7"/>
+      <c r="E1314" s="8" t="s">
+        <v>3056</v>
+      </c>
+      <c r="F1314" s="7"/>
       <c r="G1314" s="7"/>
       <c r="H1314" s="8"/>
       <c r="I1314" s="8"/>
-      <c r="J1314" s="10" t="s">
-        <v>3097</v>
-      </c>
+      <c r="J1314" s="8"/>
     </row>
     <row r="1315" s="3" customFormat="1" customHeight="1" spans="1:10">
-      <c r="A1315" s="7">
-        <v>29</v>
-      </c>
+      <c r="A1315" s="7"/>
       <c r="B1315" s="8" t="s">
-        <v>3100</v>
+        <v>3057</v>
       </c>
       <c r="C1315" s="7"/>
-      <c r="D1315" s="7">
-        <v>1777</v>
-      </c>
-      <c r="E1315" s="10" t="s">
-        <v>3075</v>
-      </c>
-      <c r="F1315" s="7" t="s">
+      <c r="D1315" s="7"/>
+      <c r="E1315" s="8" t="s">
         <v>3058</v>
       </c>
+      <c r="F1315" s="7"/>
       <c r="G1315" s="7"/>
       <c r="H1315" s="8"/>
-      <c r="I1315" s="8" t="s">
-        <v>3101</v>
-      </c>
-      <c r="J1315" s="10" t="s">
-        <v>3102</v>
-      </c>
-    </row>
-    <row r="1316" customHeight="1" spans="1:10">
-      <c r="A1316" s="7">
-        <v>30</v>
-      </c>
+      <c r="I1315" s="8"/>
+      <c r="J1315" s="8"/>
+    </row>
+    <row r="1316" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1316" s="7"/>
       <c r="B1316" s="8" t="s">
-        <v>3103</v>
+        <v>3059</v>
       </c>
       <c r="C1316" s="7"/>
-      <c r="D1316" s="7">
-        <v>1762</v>
-      </c>
+      <c r="D1316" s="7"/>
       <c r="E1316" s="8" t="s">
-        <v>3104</v>
+        <v>3060</v>
       </c>
       <c r="F1316" s="7"/>
       <c r="G1316" s="7"/>
-      <c r="H1316" s="8" t="s">
-        <v>3105</v>
-      </c>
+      <c r="H1316" s="8"/>
       <c r="I1316" s="8"/>
-      <c r="J1316" s="8" t="s">
-        <v>3106</v>
-      </c>
-    </row>
-    <row r="1317" customHeight="1" spans="1:10">
-      <c r="A1317" s="7">
-        <v>30</v>
-      </c>
+      <c r="J1316" s="8"/>
+    </row>
+    <row r="1317" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1317" s="7"/>
       <c r="B1317" s="8" t="s">
-        <v>3107</v>
+        <v>3061</v>
       </c>
       <c r="C1317" s="7"/>
-      <c r="D1317" s="7">
-        <v>1774</v>
-      </c>
+      <c r="D1317" s="7"/>
       <c r="E1317" s="8" t="s">
-        <v>3108</v>
+        <v>3062</v>
       </c>
       <c r="F1317" s="7"/>
       <c r="G1317" s="7"/>
       <c r="H1317" s="8"/>
       <c r="I1317" s="8"/>
-      <c r="J1317" s="8" t="s">
-        <v>3109</v>
-      </c>
-    </row>
-    <row r="1318" customHeight="1" spans="1:10">
-      <c r="A1318" s="7">
-        <v>30</v>
-      </c>
+      <c r="J1317" s="8"/>
+    </row>
+    <row r="1318" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1318" s="7"/>
       <c r="B1318" s="8" t="s">
-        <v>3110</v>
+        <v>3063</v>
       </c>
       <c r="C1318" s="7"/>
       <c r="D1318" s="7"/>
-      <c r="E1318" s="10" t="s">
-        <v>3111</v>
+      <c r="E1318" s="8" t="s">
+        <v>3064</v>
       </c>
       <c r="F1318" s="7"/>
       <c r="G1318" s="7"/>
-      <c r="H1318" s="8" t="s">
-        <v>3112</v>
-      </c>
+      <c r="H1318" s="8"/>
       <c r="I1318" s="8"/>
-      <c r="J1318" s="8" t="s">
-        <v>3113</v>
-      </c>
-    </row>
-    <row r="1319" customHeight="1" spans="1:10">
-      <c r="A1319" s="7">
-        <v>30</v>
-      </c>
+      <c r="J1318" s="8"/>
+    </row>
+    <row r="1319" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1319" s="7"/>
       <c r="B1319" s="8" t="s">
-        <v>3114</v>
+        <v>3065</v>
       </c>
       <c r="C1319" s="7"/>
-      <c r="D1319" s="7">
-        <v>1793</v>
-      </c>
+      <c r="D1319" s="7"/>
       <c r="E1319" s="8" t="s">
-        <v>3115</v>
-      </c>
-      <c r="F1319" s="7" t="s">
-        <v>3116</v>
-      </c>
+        <v>3066</v>
+      </c>
+      <c r="F1319" s="7"/>
       <c r="G1319" s="7"/>
-      <c r="H1319" s="8" t="s">
-        <v>3117</v>
-      </c>
-      <c r="I1319" s="8" t="s">
-        <v>3118</v>
-      </c>
-      <c r="J1319" s="8" t="s">
-        <v>3119</v>
-      </c>
-    </row>
-    <row r="1320" customHeight="1" spans="1:10">
-      <c r="A1320" s="7">
-        <v>30</v>
-      </c>
+      <c r="H1319" s="8"/>
+      <c r="I1319" s="8"/>
+      <c r="J1319" s="8"/>
+    </row>
+    <row r="1320" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1320" s="7"/>
       <c r="B1320" s="8" t="s">
-        <v>3120</v>
+        <v>3067</v>
       </c>
       <c r="C1320" s="7"/>
-      <c r="D1320" s="7">
-        <v>1796</v>
-      </c>
+      <c r="D1320" s="7"/>
       <c r="E1320" s="8" t="s">
-        <v>3121</v>
+        <v>3068</v>
       </c>
       <c r="F1320" s="7"/>
       <c r="G1320" s="7"/>
       <c r="H1320" s="8"/>
       <c r="I1320" s="8"/>
-      <c r="J1320" s="8" t="s">
-        <v>3122</v>
-      </c>
-    </row>
-    <row r="1321" customHeight="1" spans="1:10">
-      <c r="A1321" s="7">
-        <v>30</v>
-      </c>
+      <c r="J1320" s="8"/>
+    </row>
+    <row r="1321" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1321" s="7"/>
       <c r="B1321" s="8" t="s">
-        <v>3123</v>
+        <v>3069</v>
       </c>
       <c r="C1321" s="7"/>
-      <c r="D1321" s="7">
-        <v>1796</v>
-      </c>
+      <c r="D1321" s="7"/>
       <c r="E1321" s="8" t="s">
-        <v>3124</v>
+        <v>3070</v>
       </c>
       <c r="F1321" s="7"/>
-      <c r="G1321" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H1321" s="8" t="s">
-        <v>3125</v>
-      </c>
+      <c r="G1321" s="7"/>
+      <c r="H1321" s="8"/>
       <c r="I1321" s="8"/>
-      <c r="J1321" s="8" t="s">
-        <v>3126</v>
-      </c>
-    </row>
-    <row r="1322" customHeight="1" spans="1:10">
-      <c r="A1322" s="7">
-        <v>30</v>
-      </c>
+      <c r="J1321" s="8"/>
+    </row>
+    <row r="1322" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1322" s="7"/>
       <c r="B1322" s="8" t="s">
-        <v>3127</v>
+        <v>3071</v>
       </c>
       <c r="C1322" s="7"/>
-      <c r="D1322" s="7">
-        <v>1796</v>
-      </c>
+      <c r="D1322" s="7"/>
       <c r="E1322" s="8" t="s">
-        <v>3128</v>
-      </c>
-      <c r="F1322" s="7" t="s">
-        <v>3129</v>
-      </c>
-      <c r="G1322" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="H1322" s="9" t="s">
-        <v>3130</v>
-      </c>
-      <c r="I1322" s="8" t="s">
-        <v>3131</v>
-      </c>
-      <c r="J1322" s="8" t="s">
-        <v>3132</v>
-      </c>
-    </row>
-    <row r="1323" customHeight="1" spans="1:10">
-      <c r="A1323" s="7">
-        <v>30</v>
-      </c>
+        <v>3072</v>
+      </c>
+      <c r="F1322" s="7"/>
+      <c r="G1322" s="7"/>
+      <c r="H1322" s="8"/>
+      <c r="I1322" s="8"/>
+      <c r="J1322" s="8"/>
+    </row>
+    <row r="1323" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1323" s="7"/>
       <c r="B1323" s="8" t="s">
-        <v>3133</v>
+        <v>3073</v>
       </c>
       <c r="C1323" s="7"/>
-      <c r="D1323" s="7">
-        <v>1796</v>
-      </c>
+      <c r="D1323" s="7"/>
       <c r="E1323" s="8" t="s">
-        <v>3134</v>
+        <v>3074</v>
       </c>
       <c r="F1323" s="7"/>
-      <c r="G1323" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H1323" s="8" t="s">
-        <v>3135</v>
-      </c>
+      <c r="G1323" s="7"/>
+      <c r="H1323" s="8"/>
       <c r="I1323" s="8"/>
-      <c r="J1323" s="8" t="s">
-        <v>3136</v>
-      </c>
-    </row>
-    <row r="1324" customHeight="1" spans="1:10">
-      <c r="A1324" s="7">
-        <v>30</v>
-      </c>
+      <c r="J1323" s="8"/>
+    </row>
+    <row r="1324" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1324" s="7"/>
       <c r="B1324" s="8" t="s">
-        <v>3137</v>
+        <v>3075</v>
       </c>
       <c r="C1324" s="7"/>
-      <c r="D1324" s="7">
-        <v>1806</v>
-      </c>
-      <c r="E1324" s="10" t="s">
-        <v>3138</v>
+      <c r="D1324" s="7"/>
+      <c r="E1324" s="8" t="s">
+        <v>3076</v>
       </c>
       <c r="F1324" s="7"/>
       <c r="G1324" s="7"/>
       <c r="H1324" s="8"/>
       <c r="I1324" s="8"/>
-      <c r="J1324" s="10" t="s">
-        <v>3139</v>
-      </c>
-    </row>
-    <row r="1325" customHeight="1" spans="1:10">
-      <c r="A1325" s="7">
-        <v>30</v>
-      </c>
+      <c r="J1324" s="8"/>
+    </row>
+    <row r="1325" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1325" s="7"/>
       <c r="B1325" s="8" t="s">
-        <v>3140</v>
+        <v>3077</v>
       </c>
       <c r="C1325" s="7"/>
-      <c r="D1325" s="7" t="s">
-        <v>3141</v>
-      </c>
-      <c r="E1325" s="10" t="s">
-        <v>3142</v>
+      <c r="D1325" s="7"/>
+      <c r="E1325" s="8" t="s">
+        <v>3078</v>
       </c>
       <c r="F1325" s="7"/>
       <c r="G1325" s="7"/>
       <c r="H1325" s="8"/>
       <c r="I1325" s="8"/>
-      <c r="J1325" s="10" t="s">
-        <v>3143</v>
-      </c>
-    </row>
-    <row r="1326" customHeight="1" spans="1:10">
-      <c r="A1326" s="7">
-        <v>30</v>
-      </c>
+      <c r="J1325" s="8"/>
+    </row>
+    <row r="1326" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1326" s="7"/>
       <c r="B1326" s="8" t="s">
-        <v>3144</v>
+        <v>3079</v>
       </c>
       <c r="C1326" s="7"/>
-      <c r="D1326" s="7" t="s">
-        <v>3145</v>
-      </c>
-      <c r="E1326" s="10" t="s">
-        <v>3146</v>
+      <c r="D1326" s="7"/>
+      <c r="E1326" s="8" t="s">
+        <v>3080</v>
       </c>
       <c r="F1326" s="7"/>
       <c r="G1326" s="7"/>
       <c r="H1326" s="8"/>
       <c r="I1326" s="8"/>
-      <c r="J1326" s="10" t="s">
-        <v>3147</v>
-      </c>
-    </row>
-    <row r="1327" customHeight="1" spans="1:10">
-      <c r="A1327" s="7">
-        <v>30</v>
-      </c>
+      <c r="J1326" s="8"/>
+    </row>
+    <row r="1327" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1327" s="7"/>
       <c r="B1327" s="8" t="s">
-        <v>3148</v>
+        <v>3081</v>
       </c>
       <c r="C1327" s="7"/>
-      <c r="D1327" s="7" t="s">
-        <v>3149</v>
-      </c>
-      <c r="E1327" s="10" t="s">
-        <v>3150</v>
+      <c r="D1327" s="7"/>
+      <c r="E1327" s="8" t="s">
+        <v>3082</v>
       </c>
       <c r="F1327" s="7"/>
       <c r="G1327" s="7"/>
       <c r="H1327" s="8"/>
       <c r="I1327" s="8"/>
-      <c r="J1327" s="10" t="s">
+      <c r="J1327" s="8"/>
+    </row>
+    <row r="1328" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1328" s="7"/>
+      <c r="B1328" s="8" t="s">
+        <v>3083</v>
+      </c>
+      <c r="C1328" s="7"/>
+      <c r="D1328" s="7"/>
+      <c r="E1328" s="8" t="s">
+        <v>3084</v>
+      </c>
+      <c r="F1328" s="7"/>
+      <c r="G1328" s="7"/>
+      <c r="H1328" s="8"/>
+      <c r="I1328" s="8"/>
+      <c r="J1328" s="8"/>
+    </row>
+    <row r="1329" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1329" s="7"/>
+      <c r="B1329" s="8" t="s">
+        <v>3085</v>
+      </c>
+      <c r="C1329" s="7"/>
+      <c r="D1329" s="7"/>
+      <c r="E1329" s="8" t="s">
+        <v>3086</v>
+      </c>
+      <c r="F1329" s="7"/>
+      <c r="G1329" s="7"/>
+      <c r="H1329" s="8"/>
+      <c r="I1329" s="8"/>
+      <c r="J1329" s="8"/>
+    </row>
+    <row r="1330" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1330" s="7"/>
+      <c r="B1330" s="8" t="s">
+        <v>3087</v>
+      </c>
+      <c r="C1330" s="7"/>
+      <c r="D1330" s="7"/>
+      <c r="E1330" s="8" t="s">
+        <v>3088</v>
+      </c>
+      <c r="F1330" s="7"/>
+      <c r="G1330" s="7"/>
+      <c r="H1330" s="8"/>
+      <c r="I1330" s="8"/>
+      <c r="J1330" s="8"/>
+    </row>
+    <row r="1331" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1331" s="7"/>
+      <c r="B1331" s="8" t="s">
+        <v>3089</v>
+      </c>
+      <c r="C1331" s="7"/>
+      <c r="D1331" s="7"/>
+      <c r="E1331" s="8" t="s">
+        <v>3090</v>
+      </c>
+      <c r="F1331" s="7"/>
+      <c r="G1331" s="7"/>
+      <c r="H1331" s="8"/>
+      <c r="I1331" s="8"/>
+      <c r="J1331" s="8"/>
+    </row>
+    <row r="1332" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1332" s="7"/>
+      <c r="B1332" s="8" t="s">
+        <v>3091</v>
+      </c>
+      <c r="C1332" s="7"/>
+      <c r="D1332" s="7"/>
+      <c r="E1332" s="8" t="s">
+        <v>3092</v>
+      </c>
+      <c r="F1332" s="7"/>
+      <c r="G1332" s="7"/>
+      <c r="H1332" s="8"/>
+      <c r="I1332" s="8"/>
+      <c r="J1332" s="8"/>
+    </row>
+    <row r="1333" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1333" s="7"/>
+      <c r="B1333" s="8" t="s">
+        <v>3093</v>
+      </c>
+      <c r="C1333" s="7"/>
+      <c r="D1333" s="7"/>
+      <c r="E1333" s="8" t="s">
+        <v>3094</v>
+      </c>
+      <c r="F1333" s="7"/>
+      <c r="G1333" s="7"/>
+      <c r="H1333" s="8"/>
+      <c r="I1333" s="8"/>
+      <c r="J1333" s="8"/>
+    </row>
+    <row r="1334" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1334" s="7"/>
+      <c r="B1334" s="8" t="s">
+        <v>3095</v>
+      </c>
+      <c r="C1334" s="7"/>
+      <c r="D1334" s="7"/>
+      <c r="E1334" s="8" t="s">
+        <v>3096</v>
+      </c>
+      <c r="F1334" s="7"/>
+      <c r="G1334" s="7"/>
+      <c r="H1334" s="8"/>
+      <c r="I1334" s="8"/>
+      <c r="J1334" s="8"/>
+    </row>
+    <row r="1335" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1335" s="7"/>
+      <c r="B1335" s="8" t="s">
+        <v>3097</v>
+      </c>
+      <c r="C1335" s="7"/>
+      <c r="D1335" s="7"/>
+      <c r="E1335" s="8" t="s">
+        <v>3098</v>
+      </c>
+      <c r="F1335" s="7"/>
+      <c r="G1335" s="7"/>
+      <c r="H1335" s="8"/>
+      <c r="I1335" s="8"/>
+      <c r="J1335" s="8"/>
+    </row>
+    <row r="1336" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1336" s="7"/>
+      <c r="B1336" s="8" t="s">
+        <v>3099</v>
+      </c>
+      <c r="C1336" s="7"/>
+      <c r="D1336" s="7"/>
+      <c r="E1336" s="8" t="s">
+        <v>3100</v>
+      </c>
+      <c r="F1336" s="7"/>
+      <c r="G1336" s="7"/>
+      <c r="H1336" s="8"/>
+      <c r="I1336" s="8"/>
+      <c r="J1336" s="8"/>
+    </row>
+    <row r="1337" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1337" s="7"/>
+      <c r="B1337" s="8" t="s">
+        <v>3101</v>
+      </c>
+      <c r="C1337" s="7"/>
+      <c r="D1337" s="7"/>
+      <c r="E1337" s="8" t="s">
+        <v>3102</v>
+      </c>
+      <c r="F1337" s="7"/>
+      <c r="G1337" s="7"/>
+      <c r="H1337" s="8"/>
+      <c r="I1337" s="8"/>
+      <c r="J1337" s="8"/>
+    </row>
+    <row r="1338" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1338" s="7"/>
+      <c r="B1338" s="8" t="s">
+        <v>3103</v>
+      </c>
+      <c r="C1338" s="7"/>
+      <c r="D1338" s="7"/>
+      <c r="E1338" s="8" t="s">
+        <v>3104</v>
+      </c>
+      <c r="F1338" s="7"/>
+      <c r="G1338" s="7"/>
+      <c r="H1338" s="8"/>
+      <c r="I1338" s="8"/>
+      <c r="J1338" s="8"/>
+    </row>
+    <row r="1339" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1339" s="7"/>
+      <c r="B1339" s="8" t="s">
+        <v>3105</v>
+      </c>
+      <c r="C1339" s="7"/>
+      <c r="D1339" s="7"/>
+      <c r="E1339" s="8" t="s">
+        <v>3106</v>
+      </c>
+      <c r="F1339" s="7"/>
+      <c r="G1339" s="7"/>
+      <c r="H1339" s="8"/>
+      <c r="I1339" s="8"/>
+      <c r="J1339" s="8"/>
+    </row>
+    <row r="1340" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1340" s="7"/>
+      <c r="B1340" s="8" t="s">
+        <v>3107</v>
+      </c>
+      <c r="C1340" s="7"/>
+      <c r="D1340" s="7"/>
+      <c r="E1340" s="8" t="s">
+        <v>3108</v>
+      </c>
+      <c r="F1340" s="7"/>
+      <c r="G1340" s="7"/>
+      <c r="H1340" s="8"/>
+      <c r="I1340" s="8"/>
+      <c r="J1340" s="8"/>
+    </row>
+    <row r="1341" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1341" s="7"/>
+      <c r="B1341" s="8" t="s">
+        <v>3109</v>
+      </c>
+      <c r="C1341" s="7"/>
+      <c r="D1341" s="7"/>
+      <c r="E1341" s="8" t="s">
+        <v>3110</v>
+      </c>
+      <c r="F1341" s="7"/>
+      <c r="G1341" s="7"/>
+      <c r="H1341" s="8"/>
+      <c r="I1341" s="8"/>
+      <c r="J1341" s="8"/>
+    </row>
+    <row r="1342" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1342" s="7"/>
+      <c r="B1342" s="8" t="s">
+        <v>3111</v>
+      </c>
+      <c r="C1342" s="7"/>
+      <c r="D1342" s="7"/>
+      <c r="E1342" s="8" t="s">
+        <v>3112</v>
+      </c>
+      <c r="F1342" s="7"/>
+      <c r="G1342" s="7"/>
+      <c r="H1342" s="8"/>
+      <c r="I1342" s="8"/>
+      <c r="J1342" s="8"/>
+    </row>
+    <row r="1343" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1343" s="7"/>
+      <c r="B1343" s="8" t="s">
+        <v>3113</v>
+      </c>
+      <c r="C1343" s="7"/>
+      <c r="D1343" s="7"/>
+      <c r="E1343" s="8" t="s">
+        <v>3114</v>
+      </c>
+      <c r="F1343" s="7"/>
+      <c r="G1343" s="7"/>
+      <c r="H1343" s="8"/>
+      <c r="I1343" s="8"/>
+      <c r="J1343" s="8"/>
+    </row>
+    <row r="1344" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1344" s="7"/>
+      <c r="B1344" s="8" t="s">
+        <v>3115</v>
+      </c>
+      <c r="C1344" s="7"/>
+      <c r="D1344" s="7"/>
+      <c r="E1344" s="8" t="s">
+        <v>3116</v>
+      </c>
+      <c r="F1344" s="7"/>
+      <c r="G1344" s="7"/>
+      <c r="H1344" s="8"/>
+      <c r="I1344" s="8"/>
+      <c r="J1344" s="8"/>
+    </row>
+    <row r="1345" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1345" s="7"/>
+      <c r="B1345" s="8" t="s">
+        <v>3117</v>
+      </c>
+      <c r="C1345" s="7"/>
+      <c r="D1345" s="7"/>
+      <c r="E1345" s="8" t="s">
+        <v>3118</v>
+      </c>
+      <c r="F1345" s="7"/>
+      <c r="G1345" s="7"/>
+      <c r="H1345" s="8"/>
+      <c r="I1345" s="8"/>
+      <c r="J1345" s="8"/>
+    </row>
+    <row r="1346" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1346" s="7"/>
+      <c r="B1346" s="8" t="s">
+        <v>3119</v>
+      </c>
+      <c r="C1346" s="7"/>
+      <c r="D1346" s="7"/>
+      <c r="E1346" s="8" t="s">
+        <v>3120</v>
+      </c>
+      <c r="F1346" s="7"/>
+      <c r="G1346" s="7"/>
+      <c r="H1346" s="8"/>
+      <c r="I1346" s="8"/>
+      <c r="J1346" s="8"/>
+    </row>
+    <row r="1347" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1347" s="7"/>
+      <c r="B1347" s="8" t="s">
+        <v>3121</v>
+      </c>
+      <c r="C1347" s="7"/>
+      <c r="D1347" s="7"/>
+      <c r="E1347" s="8" t="s">
+        <v>3122</v>
+      </c>
+      <c r="F1347" s="7"/>
+      <c r="G1347" s="7"/>
+      <c r="H1347" s="8"/>
+      <c r="I1347" s="8"/>
+      <c r="J1347" s="8"/>
+    </row>
+    <row r="1348" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1348" s="7"/>
+      <c r="B1348" s="8" t="s">
+        <v>3123</v>
+      </c>
+      <c r="C1348" s="7"/>
+      <c r="D1348" s="7"/>
+      <c r="E1348" s="8" t="s">
+        <v>3124</v>
+      </c>
+      <c r="F1348" s="7"/>
+      <c r="G1348" s="7"/>
+      <c r="H1348" s="8"/>
+      <c r="I1348" s="8"/>
+      <c r="J1348" s="8"/>
+    </row>
+    <row r="1349" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1349" s="7"/>
+      <c r="B1349" s="8" t="s">
+        <v>3125</v>
+      </c>
+      <c r="C1349" s="7"/>
+      <c r="D1349" s="7"/>
+      <c r="E1349" s="8" t="s">
+        <v>3126</v>
+      </c>
+      <c r="F1349" s="7"/>
+      <c r="G1349" s="7"/>
+      <c r="H1349" s="8"/>
+      <c r="I1349" s="8"/>
+      <c r="J1349" s="8"/>
+    </row>
+    <row r="1350" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1350" s="7"/>
+      <c r="B1350" s="8" t="s">
+        <v>3127</v>
+      </c>
+      <c r="C1350" s="7"/>
+      <c r="D1350" s="7"/>
+      <c r="E1350" s="8" t="s">
+        <v>3128</v>
+      </c>
+      <c r="F1350" s="7"/>
+      <c r="G1350" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1350" s="8"/>
+      <c r="I1350" s="8" t="s">
+        <v>3129</v>
+      </c>
+      <c r="J1350" s="8"/>
+    </row>
+    <row r="1351" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1351" s="7"/>
+      <c r="B1351" s="8" t="s">
+        <v>3130</v>
+      </c>
+      <c r="C1351" s="7"/>
+      <c r="D1351" s="7"/>
+      <c r="E1351" s="8" t="s">
+        <v>3131</v>
+      </c>
+      <c r="F1351" s="7"/>
+      <c r="G1351" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="H1351" s="8"/>
+      <c r="I1351" s="8" t="s">
+        <v>3132</v>
+      </c>
+      <c r="J1351" s="8"/>
+    </row>
+    <row r="1352" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1352" s="7"/>
+      <c r="B1352" s="8" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C1352" s="7"/>
+      <c r="D1352" s="7"/>
+      <c r="E1352" s="8" t="s">
+        <v>3134</v>
+      </c>
+      <c r="F1352" s="7"/>
+      <c r="G1352" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1352" s="8"/>
+      <c r="I1352" s="8" t="s">
+        <v>3135</v>
+      </c>
+      <c r="J1352" s="8"/>
+    </row>
+    <row r="1353" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1353" s="7"/>
+      <c r="B1353" s="8" t="s">
+        <v>3136</v>
+      </c>
+      <c r="C1353" s="7"/>
+      <c r="D1353" s="7"/>
+      <c r="E1353" s="8" t="s">
+        <v>3137</v>
+      </c>
+      <c r="F1353" s="7"/>
+      <c r="G1353" s="7"/>
+      <c r="H1353" s="8"/>
+      <c r="I1353" s="8" t="s">
+        <v>3138</v>
+      </c>
+      <c r="J1353" s="8"/>
+    </row>
+    <row r="1354" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1354" s="7"/>
+      <c r="B1354" s="8" t="s">
+        <v>3139</v>
+      </c>
+      <c r="C1354" s="7"/>
+      <c r="D1354" s="7"/>
+      <c r="E1354" s="8" t="s">
+        <v>3128</v>
+      </c>
+      <c r="F1354" s="7"/>
+      <c r="G1354" s="7"/>
+      <c r="H1354" s="8"/>
+      <c r="I1354" s="8" t="s">
+        <v>3140</v>
+      </c>
+      <c r="J1354" s="8"/>
+    </row>
+    <row r="1355" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1355" s="7"/>
+      <c r="B1355" s="8" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1355" s="7"/>
+      <c r="D1355" s="7"/>
+      <c r="E1355" s="8" t="s">
+        <v>3142</v>
+      </c>
+      <c r="F1355" s="7"/>
+      <c r="G1355" s="7"/>
+      <c r="H1355" s="8"/>
+      <c r="I1355" s="8" t="s">
+        <v>3143</v>
+      </c>
+      <c r="J1355" s="8"/>
+    </row>
+    <row r="1356" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1356" s="7"/>
+      <c r="B1356" s="8" t="s">
+        <v>3144</v>
+      </c>
+      <c r="C1356" s="7"/>
+      <c r="D1356" s="7"/>
+      <c r="E1356" s="8" t="s">
+        <v>3145</v>
+      </c>
+      <c r="F1356" s="7"/>
+      <c r="G1356" s="7"/>
+      <c r="H1356" s="8"/>
+      <c r="I1356" s="8"/>
+      <c r="J1356" s="8"/>
+    </row>
+    <row r="1357" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1357" s="7"/>
+      <c r="B1357" s="8" t="s">
+        <v>3146</v>
+      </c>
+      <c r="C1357" s="7"/>
+      <c r="D1357" s="7"/>
+      <c r="E1357" s="8" t="s">
+        <v>3147</v>
+      </c>
+      <c r="F1357" s="7"/>
+      <c r="G1357" s="7"/>
+      <c r="H1357" s="8"/>
+      <c r="I1357" s="8"/>
+      <c r="J1357" s="8"/>
+    </row>
+    <row r="1358" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1358" s="7"/>
+      <c r="B1358" s="8" t="s">
+        <v>3148</v>
+      </c>
+      <c r="C1358" s="7"/>
+      <c r="D1358" s="7"/>
+      <c r="E1358" s="8" t="s">
+        <v>3149</v>
+      </c>
+      <c r="F1358" s="7"/>
+      <c r="G1358" s="7"/>
+      <c r="H1358" s="8"/>
+      <c r="I1358" s="8"/>
+      <c r="J1358" s="8"/>
+    </row>
+    <row r="1359" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1359" s="7"/>
+      <c r="B1359" s="8" t="s">
+        <v>3150</v>
+      </c>
+      <c r="C1359" s="7"/>
+      <c r="D1359" s="7"/>
+      <c r="E1359" s="8" t="s">
         <v>3151</v>
       </c>
-    </row>
-    <row r="1328" customHeight="1" spans="1:10">
-      <c r="A1328" s="7">
+      <c r="F1359" s="7"/>
+      <c r="G1359" s="7"/>
+      <c r="H1359" s="8"/>
+      <c r="I1359" s="8"/>
+      <c r="J1359" s="8"/>
+    </row>
+    <row r="1360" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1360" s="7"/>
+      <c r="B1360" s="8" t="s">
+        <v>3152</v>
+      </c>
+      <c r="C1360" s="7"/>
+      <c r="D1360" s="7"/>
+      <c r="E1360" s="8" t="s">
+        <v>3147</v>
+      </c>
+      <c r="F1360" s="7"/>
+      <c r="G1360" s="7"/>
+      <c r="H1360" s="8"/>
+      <c r="I1360" s="8"/>
+      <c r="J1360" s="8"/>
+    </row>
+    <row r="1361" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1361" s="7"/>
+      <c r="B1361" s="8" t="s">
+        <v>3153</v>
+      </c>
+      <c r="C1361" s="7"/>
+      <c r="D1361" s="7"/>
+      <c r="E1361" s="8" t="s">
+        <v>3154</v>
+      </c>
+      <c r="F1361" s="7"/>
+      <c r="G1361" s="7"/>
+      <c r="H1361" s="8"/>
+      <c r="I1361" s="8"/>
+      <c r="J1361" s="8"/>
+    </row>
+    <row r="1362" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1362" s="7"/>
+      <c r="B1362" s="8" t="s">
+        <v>3155</v>
+      </c>
+      <c r="C1362" s="7"/>
+      <c r="D1362" s="7"/>
+      <c r="E1362" s="8" t="s">
+        <v>3156</v>
+      </c>
+      <c r="F1362" s="7"/>
+      <c r="G1362" s="7"/>
+      <c r="H1362" s="8"/>
+      <c r="I1362" s="8"/>
+      <c r="J1362" s="8"/>
+    </row>
+    <row r="1363" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1363" s="7"/>
+      <c r="B1363" s="8" t="s">
+        <v>3157</v>
+      </c>
+      <c r="C1363" s="7"/>
+      <c r="D1363" s="7"/>
+      <c r="E1363" s="8" t="s">
+        <v>3158</v>
+      </c>
+      <c r="F1363" s="7"/>
+      <c r="G1363" s="7"/>
+      <c r="H1363" s="8"/>
+      <c r="I1363" s="8"/>
+      <c r="J1363" s="8"/>
+    </row>
+    <row r="1364" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1364" s="7"/>
+      <c r="B1364" s="8" t="s">
+        <v>3159</v>
+      </c>
+      <c r="C1364" s="7"/>
+      <c r="D1364" s="7"/>
+      <c r="E1364" s="8" t="s">
+        <v>3151</v>
+      </c>
+      <c r="F1364" s="7"/>
+      <c r="G1364" s="7"/>
+      <c r="H1364" s="8"/>
+      <c r="I1364" s="8"/>
+      <c r="J1364" s="8"/>
+    </row>
+    <row r="1365" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1365" s="7"/>
+      <c r="B1365" s="8" t="s">
+        <v>3160</v>
+      </c>
+      <c r="C1365" s="7"/>
+      <c r="D1365" s="7"/>
+      <c r="E1365" s="8" t="s">
+        <v>3147</v>
+      </c>
+      <c r="F1365" s="7"/>
+      <c r="G1365" s="7"/>
+      <c r="H1365" s="8"/>
+      <c r="I1365" s="8"/>
+      <c r="J1365" s="8"/>
+    </row>
+    <row r="1366" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1366" s="7"/>
+      <c r="B1366" s="8" t="s">
+        <v>3161</v>
+      </c>
+      <c r="C1366" s="7"/>
+      <c r="D1366" s="7"/>
+      <c r="E1366" s="8" t="s">
+        <v>3158</v>
+      </c>
+      <c r="F1366" s="7"/>
+      <c r="G1366" s="7"/>
+      <c r="H1366" s="8"/>
+      <c r="I1366" s="8"/>
+      <c r="J1366" s="8"/>
+    </row>
+    <row r="1367" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1367" s="7"/>
+      <c r="B1367" s="8" t="s">
+        <v>3162</v>
+      </c>
+      <c r="C1367" s="7"/>
+      <c r="D1367" s="7"/>
+      <c r="E1367" s="8" t="s">
+        <v>3147</v>
+      </c>
+      <c r="F1367" s="7"/>
+      <c r="G1367" s="7"/>
+      <c r="H1367" s="8"/>
+      <c r="I1367" s="8"/>
+      <c r="J1367" s="8"/>
+    </row>
+    <row r="1368" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1368" s="7"/>
+      <c r="B1368" s="8" t="s">
+        <v>3163</v>
+      </c>
+      <c r="C1368" s="7"/>
+      <c r="D1368" s="7"/>
+      <c r="E1368" s="8" t="s">
+        <v>3164</v>
+      </c>
+      <c r="F1368" s="7"/>
+      <c r="G1368" s="7"/>
+      <c r="H1368" s="8"/>
+      <c r="I1368" s="8"/>
+      <c r="J1368" s="8"/>
+    </row>
+    <row r="1369" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1369" s="7"/>
+      <c r="B1369" s="8" t="s">
+        <v>3165</v>
+      </c>
+      <c r="C1369" s="7"/>
+      <c r="D1369" s="7"/>
+      <c r="E1369" s="8" t="s">
+        <v>3166</v>
+      </c>
+      <c r="F1369" s="7"/>
+      <c r="G1369" s="7"/>
+      <c r="H1369" s="8"/>
+      <c r="I1369" s="8"/>
+      <c r="J1369" s="8"/>
+    </row>
+    <row r="1370" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1370" s="7"/>
+      <c r="B1370" s="8" t="s">
+        <v>3167</v>
+      </c>
+      <c r="C1370" s="7"/>
+      <c r="D1370" s="7"/>
+      <c r="E1370" s="8" t="s">
+        <v>3168</v>
+      </c>
+      <c r="F1370" s="7"/>
+      <c r="G1370" s="7"/>
+      <c r="H1370" s="8"/>
+      <c r="I1370" s="8"/>
+      <c r="J1370" s="8"/>
+    </row>
+    <row r="1371" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1371" s="7"/>
+      <c r="B1371" s="8" t="s">
+        <v>3169</v>
+      </c>
+      <c r="C1371" s="7"/>
+      <c r="D1371" s="7"/>
+      <c r="E1371" s="8" t="s">
+        <v>3158</v>
+      </c>
+      <c r="F1371" s="7"/>
+      <c r="G1371" s="7"/>
+      <c r="H1371" s="8"/>
+      <c r="I1371" s="8"/>
+      <c r="J1371" s="8"/>
+    </row>
+    <row r="1372" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1372" s="7"/>
+      <c r="B1372" s="8" t="s">
+        <v>3170</v>
+      </c>
+      <c r="C1372" s="7"/>
+      <c r="D1372" s="7"/>
+      <c r="E1372" s="8" t="s">
+        <v>3128</v>
+      </c>
+      <c r="F1372" s="7"/>
+      <c r="G1372" s="7"/>
+      <c r="H1372" s="8"/>
+      <c r="I1372" s="8"/>
+      <c r="J1372" s="8"/>
+    </row>
+    <row r="1373" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1373" s="7"/>
+      <c r="B1373" s="8" t="s">
+        <v>3171</v>
+      </c>
+      <c r="C1373" s="7"/>
+      <c r="D1373" s="7"/>
+      <c r="E1373" s="8" t="s">
+        <v>3172</v>
+      </c>
+      <c r="F1373" s="7"/>
+      <c r="G1373" s="7"/>
+      <c r="H1373" s="8"/>
+      <c r="I1373" s="8"/>
+      <c r="J1373" s="8"/>
+    </row>
+    <row r="1374" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1374" s="7"/>
+      <c r="B1374" s="8" t="s">
+        <v>3173</v>
+      </c>
+      <c r="C1374" s="7"/>
+      <c r="D1374" s="7"/>
+      <c r="E1374" s="8" t="s">
+        <v>3174</v>
+      </c>
+      <c r="F1374" s="7"/>
+      <c r="G1374" s="7"/>
+      <c r="H1374" s="8"/>
+      <c r="I1374" s="8"/>
+      <c r="J1374" s="8"/>
+    </row>
+    <row r="1375" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1375" s="7"/>
+      <c r="B1375" s="8" t="s">
+        <v>3175</v>
+      </c>
+      <c r="C1375" s="7"/>
+      <c r="D1375" s="7"/>
+      <c r="E1375" s="8" t="s">
+        <v>3154</v>
+      </c>
+      <c r="F1375" s="7"/>
+      <c r="G1375" s="7"/>
+      <c r="H1375" s="8"/>
+      <c r="I1375" s="8"/>
+      <c r="J1375" s="8"/>
+    </row>
+    <row r="1376" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1376" s="7"/>
+      <c r="B1376" s="8" t="s">
+        <v>3176</v>
+      </c>
+      <c r="C1376" s="7"/>
+      <c r="D1376" s="7"/>
+      <c r="E1376" s="8" t="s">
+        <v>3145</v>
+      </c>
+      <c r="F1376" s="7"/>
+      <c r="G1376" s="7"/>
+      <c r="H1376" s="8"/>
+      <c r="I1376" s="8"/>
+      <c r="J1376" s="8"/>
+    </row>
+    <row r="1377" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1377" s="7"/>
+      <c r="B1377" s="8" t="s">
+        <v>3177</v>
+      </c>
+      <c r="C1377" s="7"/>
+      <c r="D1377" s="7"/>
+      <c r="E1377" s="8" t="s">
+        <v>3178</v>
+      </c>
+      <c r="F1377" s="7"/>
+      <c r="G1377" s="7"/>
+      <c r="H1377" s="8"/>
+      <c r="I1377" s="8"/>
+      <c r="J1377" s="8"/>
+    </row>
+    <row r="1378" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1378" s="7"/>
+      <c r="B1378" s="8" t="s">
+        <v>3179</v>
+      </c>
+      <c r="C1378" s="7"/>
+      <c r="D1378" s="7"/>
+      <c r="E1378" s="8" t="s">
+        <v>3128</v>
+      </c>
+      <c r="F1378" s="7"/>
+      <c r="G1378" s="7"/>
+      <c r="H1378" s="8"/>
+      <c r="I1378" s="8"/>
+      <c r="J1378" s="8"/>
+    </row>
+    <row r="1379" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1379" s="7"/>
+      <c r="B1379" s="8" t="s">
+        <v>3180</v>
+      </c>
+      <c r="C1379" s="7"/>
+      <c r="D1379" s="7"/>
+      <c r="E1379" s="8" t="s">
+        <v>3181</v>
+      </c>
+      <c r="F1379" s="7"/>
+      <c r="G1379" s="7"/>
+      <c r="H1379" s="8"/>
+      <c r="I1379" s="8"/>
+      <c r="J1379" s="8"/>
+    </row>
+    <row r="1380" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1380" s="7"/>
+      <c r="B1380" s="8" t="s">
+        <v>3182</v>
+      </c>
+      <c r="C1380" s="7"/>
+      <c r="D1380" s="7"/>
+      <c r="E1380" s="8" t="s">
+        <v>3151</v>
+      </c>
+      <c r="F1380" s="7"/>
+      <c r="G1380" s="7"/>
+      <c r="H1380" s="8"/>
+      <c r="I1380" s="8"/>
+      <c r="J1380" s="8"/>
+    </row>
+    <row r="1381" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1381" s="7"/>
+      <c r="B1381" s="8" t="s">
+        <v>3183</v>
+      </c>
+      <c r="C1381" s="7"/>
+      <c r="D1381" s="7"/>
+      <c r="E1381" s="8" t="s">
+        <v>3168</v>
+      </c>
+      <c r="F1381" s="7"/>
+      <c r="G1381" s="7"/>
+      <c r="H1381" s="8"/>
+      <c r="I1381" s="8"/>
+      <c r="J1381" s="8"/>
+    </row>
+    <row r="1382" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1382" s="7"/>
+      <c r="B1382" s="8" t="s">
+        <v>3184</v>
+      </c>
+      <c r="C1382" s="7"/>
+      <c r="D1382" s="7"/>
+      <c r="E1382" s="8" t="s">
+        <v>3128</v>
+      </c>
+      <c r="F1382" s="7"/>
+      <c r="G1382" s="7"/>
+      <c r="H1382" s="8"/>
+      <c r="I1382" s="8"/>
+      <c r="J1382" s="8"/>
+    </row>
+    <row r="1383" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1383" s="7"/>
+      <c r="B1383" s="8" t="s">
+        <v>3185</v>
+      </c>
+      <c r="C1383" s="7"/>
+      <c r="D1383" s="7"/>
+      <c r="E1383" s="8" t="s">
+        <v>3186</v>
+      </c>
+      <c r="F1383" s="7"/>
+      <c r="G1383" s="7"/>
+      <c r="H1383" s="8"/>
+      <c r="I1383" s="8"/>
+      <c r="J1383" s="8"/>
+    </row>
+    <row r="1384" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1384" s="7"/>
+      <c r="B1384" s="8" t="s">
+        <v>3187</v>
+      </c>
+      <c r="C1384" s="7"/>
+      <c r="D1384" s="7"/>
+      <c r="E1384" s="8" t="s">
+        <v>3188</v>
+      </c>
+      <c r="F1384" s="7"/>
+      <c r="G1384" s="7"/>
+      <c r="H1384" s="8"/>
+      <c r="I1384" s="8" t="s">
+        <v>3143</v>
+      </c>
+      <c r="J1384" s="8"/>
+    </row>
+    <row r="1385" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1385" s="7"/>
+      <c r="B1385" s="8" t="s">
+        <v>3189</v>
+      </c>
+      <c r="C1385" s="7"/>
+      <c r="D1385" s="7"/>
+      <c r="E1385" s="8" t="s">
+        <v>3190</v>
+      </c>
+      <c r="F1385" s="7"/>
+      <c r="G1385" s="7"/>
+      <c r="H1385" s="8"/>
+      <c r="I1385" s="8" t="s">
+        <v>3191</v>
+      </c>
+      <c r="J1385" s="8"/>
+    </row>
+    <row r="1386" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1386" s="7"/>
+      <c r="B1386" s="8" t="s">
+        <v>3192</v>
+      </c>
+      <c r="C1386" s="7"/>
+      <c r="D1386" s="7"/>
+      <c r="E1386" s="8" t="s">
+        <v>3193</v>
+      </c>
+      <c r="F1386" s="7"/>
+      <c r="G1386" s="7"/>
+      <c r="H1386" s="8"/>
+      <c r="I1386" s="8" t="s">
+        <v>3194</v>
+      </c>
+      <c r="J1386" s="8"/>
+    </row>
+    <row r="1387" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1387" s="7"/>
+      <c r="B1387" s="8" t="s">
+        <v>3195</v>
+      </c>
+      <c r="C1387" s="7"/>
+      <c r="D1387" s="7"/>
+      <c r="E1387" s="8" t="s">
+        <v>3196</v>
+      </c>
+      <c r="F1387" s="7"/>
+      <c r="G1387" s="7"/>
+      <c r="H1387" s="8"/>
+      <c r="I1387" s="8" t="s">
+        <v>3197</v>
+      </c>
+      <c r="J1387" s="8"/>
+    </row>
+    <row r="1388" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1388" s="7"/>
+      <c r="B1388" s="8" t="s">
+        <v>3198</v>
+      </c>
+      <c r="C1388" s="7"/>
+      <c r="D1388" s="7"/>
+      <c r="E1388" s="8" t="s">
+        <v>3199</v>
+      </c>
+      <c r="F1388" s="7"/>
+      <c r="G1388" s="7"/>
+      <c r="H1388" s="8"/>
+      <c r="I1388" s="8" t="s">
+        <v>3200</v>
+      </c>
+      <c r="J1388" s="8"/>
+    </row>
+    <row r="1389" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1389" s="7"/>
+      <c r="B1389" s="8" t="s">
+        <v>3201</v>
+      </c>
+      <c r="C1389" s="7"/>
+      <c r="D1389" s="7"/>
+      <c r="E1389" s="8" t="s">
+        <v>3202</v>
+      </c>
+      <c r="F1389" s="7"/>
+      <c r="G1389" s="7"/>
+      <c r="H1389" s="8"/>
+      <c r="I1389" s="8" t="s">
+        <v>3203</v>
+      </c>
+      <c r="J1389" s="8"/>
+    </row>
+    <row r="1390" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1390" s="7"/>
+      <c r="B1390" s="8" t="s">
+        <v>3204</v>
+      </c>
+      <c r="C1390" s="7"/>
+      <c r="D1390" s="7"/>
+      <c r="E1390" s="8" t="s">
+        <v>3205</v>
+      </c>
+      <c r="F1390" s="7"/>
+      <c r="G1390" s="7"/>
+      <c r="H1390" s="8"/>
+      <c r="I1390" s="8"/>
+      <c r="J1390" s="8"/>
+    </row>
+    <row r="1391" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1391" s="7"/>
+      <c r="B1391" s="8" t="s">
+        <v>3206</v>
+      </c>
+      <c r="C1391" s="7"/>
+      <c r="D1391" s="7"/>
+      <c r="E1391" s="8" t="s">
+        <v>3207</v>
+      </c>
+      <c r="F1391" s="7"/>
+      <c r="G1391" s="7"/>
+      <c r="H1391" s="8"/>
+      <c r="I1391" s="8"/>
+      <c r="J1391" s="8"/>
+    </row>
+    <row r="1392" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1392" s="7"/>
+      <c r="B1392" s="8" t="s">
+        <v>3208</v>
+      </c>
+      <c r="C1392" s="7"/>
+      <c r="D1392" s="7"/>
+      <c r="E1392" s="8" t="s">
+        <v>3209</v>
+      </c>
+      <c r="F1392" s="7"/>
+      <c r="G1392" s="7"/>
+      <c r="H1392" s="8"/>
+      <c r="I1392" s="8"/>
+      <c r="J1392" s="8"/>
+    </row>
+    <row r="1393" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1393" s="7"/>
+      <c r="B1393" s="8" t="s">
+        <v>3210</v>
+      </c>
+      <c r="C1393" s="7"/>
+      <c r="D1393" s="7"/>
+      <c r="E1393" s="8" t="s">
+        <v>3211</v>
+      </c>
+      <c r="F1393" s="7"/>
+      <c r="G1393" s="7"/>
+      <c r="H1393" s="8"/>
+      <c r="I1393" s="8"/>
+      <c r="J1393" s="8"/>
+    </row>
+    <row r="1394" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1394" s="7"/>
+      <c r="B1394" s="8" t="s">
+        <v>3212</v>
+      </c>
+      <c r="C1394" s="7"/>
+      <c r="D1394" s="7"/>
+      <c r="E1394" s="8" t="s">
+        <v>3213</v>
+      </c>
+      <c r="F1394" s="7"/>
+      <c r="G1394" s="7"/>
+      <c r="H1394" s="8"/>
+      <c r="I1394" s="8"/>
+      <c r="J1394" s="8"/>
+    </row>
+    <row r="1395" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1395" s="7"/>
+      <c r="B1395" s="8" t="s">
+        <v>3214</v>
+      </c>
+      <c r="C1395" s="7"/>
+      <c r="D1395" s="7"/>
+      <c r="E1395" s="8" t="s">
+        <v>3213</v>
+      </c>
+      <c r="F1395" s="7"/>
+      <c r="G1395" s="7"/>
+      <c r="H1395" s="8"/>
+      <c r="I1395" s="8"/>
+      <c r="J1395" s="8"/>
+    </row>
+    <row r="1396" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1396" s="7"/>
+      <c r="B1396" s="8" t="s">
+        <v>3215</v>
+      </c>
+      <c r="C1396" s="7"/>
+      <c r="D1396" s="7"/>
+      <c r="E1396" s="8" t="s">
+        <v>3216</v>
+      </c>
+      <c r="F1396" s="7"/>
+      <c r="G1396" s="7"/>
+      <c r="H1396" s="8"/>
+      <c r="I1396" s="8"/>
+      <c r="J1396" s="8"/>
+    </row>
+    <row r="1397" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1397" s="7"/>
+      <c r="B1397" s="8" t="s">
+        <v>3217</v>
+      </c>
+      <c r="C1397" s="7"/>
+      <c r="D1397" s="7"/>
+      <c r="E1397" s="8" t="s">
+        <v>3216</v>
+      </c>
+      <c r="F1397" s="7"/>
+      <c r="G1397" s="7"/>
+      <c r="H1397" s="8"/>
+      <c r="I1397" s="8"/>
+      <c r="J1397" s="8"/>
+    </row>
+    <row r="1398" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1398" s="7"/>
+      <c r="B1398" s="8" t="s">
+        <v>3218</v>
+      </c>
+      <c r="C1398" s="7"/>
+      <c r="D1398" s="7"/>
+      <c r="E1398" s="8" t="s">
+        <v>3213</v>
+      </c>
+      <c r="F1398" s="7"/>
+      <c r="G1398" s="7"/>
+      <c r="H1398" s="8"/>
+      <c r="I1398" s="8"/>
+      <c r="J1398" s="8"/>
+    </row>
+    <row r="1399" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1399" s="7"/>
+      <c r="B1399" s="8" t="s">
+        <v>3219</v>
+      </c>
+      <c r="C1399" s="7"/>
+      <c r="D1399" s="7"/>
+      <c r="E1399" s="8" t="s">
+        <v>3220</v>
+      </c>
+      <c r="F1399" s="7"/>
+      <c r="G1399" s="7"/>
+      <c r="H1399" s="8"/>
+      <c r="I1399" s="8"/>
+      <c r="J1399" s="8"/>
+    </row>
+    <row r="1400" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1400" s="7"/>
+      <c r="B1400" s="8" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C1400" s="7"/>
+      <c r="D1400" s="7"/>
+      <c r="E1400" s="8" t="s">
+        <v>3222</v>
+      </c>
+      <c r="F1400" s="7"/>
+      <c r="G1400" s="7"/>
+      <c r="H1400" s="8"/>
+      <c r="I1400" s="8"/>
+      <c r="J1400" s="8"/>
+    </row>
+    <row r="1401" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1401" s="7"/>
+      <c r="B1401" s="8" t="s">
+        <v>3223</v>
+      </c>
+      <c r="C1401" s="7"/>
+      <c r="D1401" s="7"/>
+      <c r="E1401" s="8" t="s">
+        <v>3224</v>
+      </c>
+      <c r="F1401" s="7"/>
+      <c r="G1401" s="7"/>
+      <c r="H1401" s="8"/>
+      <c r="I1401" s="8"/>
+      <c r="J1401" s="8"/>
+    </row>
+    <row r="1402" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1402" s="7"/>
+      <c r="B1402" s="8" t="s">
+        <v>3225</v>
+      </c>
+      <c r="C1402" s="7"/>
+      <c r="D1402" s="7"/>
+      <c r="E1402" s="8" t="s">
+        <v>3224</v>
+      </c>
+      <c r="F1402" s="7"/>
+      <c r="G1402" s="7"/>
+      <c r="H1402" s="8"/>
+      <c r="I1402" s="8"/>
+      <c r="J1402" s="8"/>
+    </row>
+    <row r="1403" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1403" s="7"/>
+      <c r="B1403" s="8" t="s">
+        <v>3226</v>
+      </c>
+      <c r="C1403" s="7"/>
+      <c r="D1403" s="7"/>
+      <c r="E1403" s="8" t="s">
+        <v>3227</v>
+      </c>
+      <c r="F1403" s="7"/>
+      <c r="G1403" s="7"/>
+      <c r="H1403" s="8"/>
+      <c r="I1403" s="8"/>
+      <c r="J1403" s="8"/>
+    </row>
+    <row r="1404" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1404" s="7"/>
+      <c r="B1404" s="8" t="s">
+        <v>3228</v>
+      </c>
+      <c r="C1404" s="7"/>
+      <c r="D1404" s="7"/>
+      <c r="E1404" s="8" t="s">
+        <v>3227</v>
+      </c>
+      <c r="F1404" s="7"/>
+      <c r="G1404" s="7"/>
+      <c r="H1404" s="8"/>
+      <c r="I1404" s="8"/>
+      <c r="J1404" s="8"/>
+    </row>
+    <row r="1405" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1405" s="7"/>
+      <c r="B1405" s="8" t="s">
+        <v>3229</v>
+      </c>
+      <c r="C1405" s="7"/>
+      <c r="D1405" s="7"/>
+      <c r="E1405" s="8" t="s">
+        <v>3230</v>
+      </c>
+      <c r="F1405" s="7"/>
+      <c r="G1405" s="7"/>
+      <c r="H1405" s="8"/>
+      <c r="I1405" s="8"/>
+      <c r="J1405" s="8"/>
+    </row>
+    <row r="1406" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1406" s="7"/>
+      <c r="B1406" s="8" t="s">
+        <v>3231</v>
+      </c>
+      <c r="C1406" s="7"/>
+      <c r="D1406" s="7"/>
+      <c r="E1406" s="8" t="s">
+        <v>3211</v>
+      </c>
+      <c r="F1406" s="7"/>
+      <c r="G1406" s="7"/>
+      <c r="H1406" s="8"/>
+      <c r="I1406" s="8"/>
+      <c r="J1406" s="8"/>
+    </row>
+    <row r="1407" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1407" s="7"/>
+      <c r="B1407" s="8" t="s">
+        <v>3232</v>
+      </c>
+      <c r="C1407" s="7"/>
+      <c r="D1407" s="7"/>
+      <c r="E1407" s="8" t="s">
+        <v>3233</v>
+      </c>
+      <c r="F1407" s="7"/>
+      <c r="G1407" s="7"/>
+      <c r="H1407" s="8"/>
+      <c r="I1407" s="8"/>
+      <c r="J1407" s="8"/>
+    </row>
+    <row r="1408" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1408" s="7"/>
+      <c r="B1408" s="8" t="s">
+        <v>3234</v>
+      </c>
+      <c r="C1408" s="7"/>
+      <c r="D1408" s="7"/>
+      <c r="E1408" s="8" t="s">
+        <v>3235</v>
+      </c>
+      <c r="F1408" s="7"/>
+      <c r="G1408" s="7"/>
+      <c r="H1408" s="8"/>
+      <c r="I1408" s="8"/>
+      <c r="J1408" s="8"/>
+    </row>
+    <row r="1409" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1409" s="7"/>
+      <c r="B1409" s="8" t="s">
+        <v>3236</v>
+      </c>
+      <c r="C1409" s="7"/>
+      <c r="D1409" s="7"/>
+      <c r="E1409" s="8" t="s">
+        <v>3211</v>
+      </c>
+      <c r="F1409" s="7"/>
+      <c r="G1409" s="7"/>
+      <c r="H1409" s="8"/>
+      <c r="I1409" s="8"/>
+      <c r="J1409" s="8"/>
+    </row>
+    <row r="1410" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1410" s="7"/>
+      <c r="B1410" s="8" t="s">
+        <v>3237</v>
+      </c>
+      <c r="C1410" s="7"/>
+      <c r="D1410" s="7"/>
+      <c r="E1410" s="8" t="s">
+        <v>3213</v>
+      </c>
+      <c r="F1410" s="7"/>
+      <c r="G1410" s="7"/>
+      <c r="H1410" s="8"/>
+      <c r="I1410" s="8"/>
+      <c r="J1410" s="8"/>
+    </row>
+    <row r="1411" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1411" s="7"/>
+      <c r="B1411" s="8" t="s">
+        <v>3238</v>
+      </c>
+      <c r="C1411" s="7"/>
+      <c r="D1411" s="7"/>
+      <c r="E1411" s="8" t="s">
+        <v>3220</v>
+      </c>
+      <c r="F1411" s="7"/>
+      <c r="G1411" s="7"/>
+      <c r="H1411" s="8"/>
+      <c r="I1411" s="8"/>
+      <c r="J1411" s="8"/>
+    </row>
+    <row r="1412" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1412" s="7"/>
+      <c r="B1412" s="8" t="s">
+        <v>3239</v>
+      </c>
+      <c r="C1412" s="7"/>
+      <c r="D1412" s="7"/>
+      <c r="E1412" s="8" t="s">
+        <v>3240</v>
+      </c>
+      <c r="F1412" s="7"/>
+      <c r="G1412" s="7"/>
+      <c r="H1412" s="8"/>
+      <c r="I1412" s="8"/>
+      <c r="J1412" s="8"/>
+    </row>
+    <row r="1413" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1413" s="7"/>
+      <c r="B1413" s="8" t="s">
+        <v>3241</v>
+      </c>
+      <c r="C1413" s="7"/>
+      <c r="D1413" s="7"/>
+      <c r="E1413" s="8" t="s">
+        <v>3242</v>
+      </c>
+      <c r="F1413" s="7"/>
+      <c r="G1413" s="7"/>
+      <c r="H1413" s="8"/>
+      <c r="I1413" s="8"/>
+      <c r="J1413" s="8"/>
+    </row>
+    <row r="1414" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1414" s="7"/>
+      <c r="B1414" s="8" t="s">
+        <v>3243</v>
+      </c>
+      <c r="C1414" s="7"/>
+      <c r="D1414" s="7"/>
+      <c r="E1414" s="8" t="s">
+        <v>3242</v>
+      </c>
+      <c r="F1414" s="7"/>
+      <c r="G1414" s="7"/>
+      <c r="H1414" s="8"/>
+      <c r="I1414" s="8"/>
+      <c r="J1414" s="8"/>
+    </row>
+    <row r="1415" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1415" s="7"/>
+      <c r="B1415" s="8" t="s">
+        <v>3244</v>
+      </c>
+      <c r="C1415" s="7"/>
+      <c r="D1415" s="7"/>
+      <c r="E1415" s="3" t="s">
+        <v>3245</v>
+      </c>
+      <c r="F1415" s="7"/>
+      <c r="G1415" s="7"/>
+      <c r="H1415" s="8"/>
+      <c r="I1415" s="8"/>
+      <c r="J1415" s="8"/>
+    </row>
+    <row r="1416" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1416" s="7"/>
+      <c r="B1416" s="8" t="s">
+        <v>3246</v>
+      </c>
+      <c r="C1416" s="7"/>
+      <c r="D1416" s="7"/>
+      <c r="E1416" s="8" t="s">
+        <v>3247</v>
+      </c>
+      <c r="F1416" s="7"/>
+      <c r="G1416" s="7"/>
+      <c r="H1416" s="8"/>
+      <c r="I1416" s="8"/>
+      <c r="J1416" s="8"/>
+    </row>
+    <row r="1417" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1417" s="7"/>
+      <c r="B1417" s="8" t="s">
+        <v>3248</v>
+      </c>
+      <c r="C1417" s="7"/>
+      <c r="D1417" s="7"/>
+      <c r="E1417" s="8" t="s">
+        <v>3220</v>
+      </c>
+      <c r="F1417" s="7"/>
+      <c r="G1417" s="7"/>
+      <c r="H1417" s="8"/>
+      <c r="I1417" s="8"/>
+      <c r="J1417" s="8"/>
+    </row>
+    <row r="1418" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1418" s="7"/>
+      <c r="B1418" s="8" t="s">
+        <v>3249</v>
+      </c>
+      <c r="C1418" s="7"/>
+      <c r="D1418" s="7"/>
+      <c r="E1418" s="8" t="s">
+        <v>3222</v>
+      </c>
+      <c r="F1418" s="7"/>
+      <c r="G1418" s="7"/>
+      <c r="H1418" s="8"/>
+      <c r="I1418" s="8"/>
+      <c r="J1418" s="8"/>
+    </row>
+    <row r="1419" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1419" s="7"/>
+      <c r="B1419" s="8" t="s">
+        <v>3250</v>
+      </c>
+      <c r="C1419" s="7"/>
+      <c r="D1419" s="7"/>
+      <c r="E1419" s="8" t="s">
+        <v>3251</v>
+      </c>
+      <c r="F1419" s="7"/>
+      <c r="G1419" s="7"/>
+      <c r="H1419" s="8"/>
+      <c r="I1419" s="8"/>
+      <c r="J1419" s="8"/>
+    </row>
+    <row r="1420" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1420" s="7"/>
+      <c r="B1420" s="8" t="s">
+        <v>3252</v>
+      </c>
+      <c r="C1420" s="7"/>
+      <c r="D1420" s="7"/>
+      <c r="E1420" s="8" t="s">
+        <v>3211</v>
+      </c>
+      <c r="F1420" s="7"/>
+      <c r="G1420" s="7"/>
+      <c r="H1420" s="8"/>
+      <c r="I1420" s="8"/>
+      <c r="J1420" s="8"/>
+    </row>
+    <row r="1421" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1421" s="7"/>
+      <c r="B1421" s="8" t="s">
+        <v>3253</v>
+      </c>
+      <c r="C1421" s="7"/>
+      <c r="D1421" s="7"/>
+      <c r="E1421" s="8" t="s">
+        <v>3254</v>
+      </c>
+      <c r="F1421" s="7"/>
+      <c r="G1421" s="7"/>
+      <c r="H1421" s="8"/>
+      <c r="I1421" s="8"/>
+      <c r="J1421" s="8"/>
+    </row>
+    <row r="1422" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1422" s="7"/>
+      <c r="B1422" s="8" t="s">
+        <v>3255</v>
+      </c>
+      <c r="C1422" s="7"/>
+      <c r="D1422" s="7"/>
+      <c r="E1422" s="8" t="s">
+        <v>3222</v>
+      </c>
+      <c r="F1422" s="7"/>
+      <c r="G1422" s="7"/>
+      <c r="H1422" s="8"/>
+      <c r="I1422" s="8"/>
+      <c r="J1422" s="8"/>
+    </row>
+    <row r="1423" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1423" s="7"/>
+      <c r="B1423" s="8" t="s">
+        <v>3256</v>
+      </c>
+      <c r="C1423" s="7"/>
+      <c r="D1423" s="7"/>
+      <c r="E1423" s="8" t="s">
+        <v>3257</v>
+      </c>
+      <c r="F1423" s="7"/>
+      <c r="G1423" s="7"/>
+      <c r="H1423" s="8"/>
+      <c r="I1423" s="8"/>
+      <c r="J1423" s="8"/>
+    </row>
+    <row r="1424" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1424" s="7"/>
+      <c r="B1424" s="8" t="s">
+        <v>3258</v>
+      </c>
+      <c r="C1424" s="7"/>
+      <c r="D1424" s="7"/>
+      <c r="E1424" s="8" t="s">
+        <v>3259</v>
+      </c>
+      <c r="F1424" s="7"/>
+      <c r="G1424" s="7"/>
+      <c r="H1424" s="8"/>
+      <c r="I1424" s="8"/>
+      <c r="J1424" s="8"/>
+    </row>
+    <row r="1425" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1425" s="7"/>
+      <c r="B1425" s="8" t="s">
+        <v>3260</v>
+      </c>
+      <c r="C1425" s="7"/>
+      <c r="D1425" s="7"/>
+      <c r="E1425" s="8" t="s">
+        <v>3261</v>
+      </c>
+      <c r="F1425" s="7"/>
+      <c r="G1425" s="7"/>
+      <c r="H1425" s="8"/>
+      <c r="I1425" s="8"/>
+      <c r="J1425" s="8"/>
+    </row>
+    <row r="1426" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1426" s="7"/>
+      <c r="B1426" s="8" t="s">
+        <v>3262</v>
+      </c>
+      <c r="C1426" s="7"/>
+      <c r="D1426" s="7"/>
+      <c r="E1426" s="8" t="s">
+        <v>3263</v>
+      </c>
+      <c r="F1426" s="7"/>
+      <c r="G1426" s="7"/>
+      <c r="H1426" s="8"/>
+      <c r="I1426" s="8"/>
+      <c r="J1426" s="8"/>
+    </row>
+    <row r="1427" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1427" s="7"/>
+      <c r="B1427" s="8" t="s">
+        <v>3264</v>
+      </c>
+      <c r="C1427" s="7"/>
+      <c r="D1427" s="7"/>
+      <c r="E1427" s="8" t="s">
+        <v>3207</v>
+      </c>
+      <c r="F1427" s="7"/>
+      <c r="G1427" s="7"/>
+      <c r="H1427" s="8"/>
+      <c r="I1427" s="8"/>
+      <c r="J1427" s="8"/>
+    </row>
+    <row r="1428" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1428" s="7"/>
+      <c r="B1428" s="8" t="s">
+        <v>3265</v>
+      </c>
+      <c r="C1428" s="7"/>
+      <c r="D1428" s="7"/>
+      <c r="E1428" s="8" t="s">
+        <v>3266</v>
+      </c>
+      <c r="F1428" s="7"/>
+      <c r="G1428" s="7"/>
+      <c r="H1428" s="8"/>
+      <c r="I1428" s="8"/>
+      <c r="J1428" s="8"/>
+    </row>
+    <row r="1429" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1429" s="7"/>
+      <c r="B1429" s="8" t="s">
+        <v>3267</v>
+      </c>
+      <c r="C1429" s="7"/>
+      <c r="D1429" s="7"/>
+      <c r="E1429" s="8" t="s">
+        <v>3268</v>
+      </c>
+      <c r="F1429" s="7"/>
+      <c r="G1429" s="7"/>
+      <c r="H1429" s="8"/>
+      <c r="I1429" s="8"/>
+      <c r="J1429" s="8"/>
+    </row>
+    <row r="1430" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1430" s="7"/>
+      <c r="B1430" s="8" t="s">
+        <v>3269</v>
+      </c>
+      <c r="C1430" s="7"/>
+      <c r="D1430" s="7"/>
+      <c r="E1430" s="8" t="s">
+        <v>3270</v>
+      </c>
+      <c r="F1430" s="7"/>
+      <c r="G1430" s="7"/>
+      <c r="H1430" s="8"/>
+      <c r="I1430" s="8"/>
+      <c r="J1430" s="8"/>
+    </row>
+    <row r="1431" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1431" s="7"/>
+      <c r="B1431" s="8" t="s">
+        <v>3271</v>
+      </c>
+      <c r="C1431" s="7"/>
+      <c r="D1431" s="7"/>
+      <c r="E1431" s="8" t="s">
+        <v>3272</v>
+      </c>
+      <c r="F1431" s="7"/>
+      <c r="G1431" s="7"/>
+      <c r="H1431" s="8"/>
+      <c r="I1431" s="8"/>
+      <c r="J1431" s="8"/>
+    </row>
+    <row r="1432" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1432" s="7"/>
+      <c r="B1432" s="8" t="s">
+        <v>3273</v>
+      </c>
+      <c r="C1432" s="7"/>
+      <c r="D1432" s="7"/>
+      <c r="E1432" s="8" t="s">
+        <v>3274</v>
+      </c>
+      <c r="F1432" s="7"/>
+      <c r="G1432" s="7"/>
+      <c r="H1432" s="8"/>
+      <c r="I1432" s="8"/>
+      <c r="J1432" s="8"/>
+    </row>
+    <row r="1433" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1433" s="7"/>
+      <c r="B1433" s="8" t="s">
+        <v>3275</v>
+      </c>
+      <c r="C1433" s="7"/>
+      <c r="D1433" s="7"/>
+      <c r="E1433" s="8" t="s">
+        <v>3276</v>
+      </c>
+      <c r="F1433" s="7"/>
+      <c r="G1433" s="7"/>
+      <c r="H1433" s="8"/>
+      <c r="I1433" s="8"/>
+      <c r="J1433" s="8"/>
+    </row>
+    <row r="1434" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1434" s="7"/>
+      <c r="B1434" s="8" t="s">
+        <v>3277</v>
+      </c>
+      <c r="C1434" s="7"/>
+      <c r="D1434" s="7"/>
+      <c r="E1434" s="8" t="s">
+        <v>3242</v>
+      </c>
+      <c r="F1434" s="7"/>
+      <c r="G1434" s="7"/>
+      <c r="H1434" s="8"/>
+      <c r="I1434" s="8"/>
+      <c r="J1434" s="8"/>
+    </row>
+    <row r="1435" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1435" s="7"/>
+      <c r="B1435" s="8" t="s">
+        <v>3278</v>
+      </c>
+      <c r="C1435" s="7"/>
+      <c r="D1435" s="7"/>
+      <c r="E1435" s="8" t="s">
+        <v>3227</v>
+      </c>
+      <c r="F1435" s="7"/>
+      <c r="G1435" s="7"/>
+      <c r="H1435" s="8"/>
+      <c r="I1435" s="8"/>
+      <c r="J1435" s="8"/>
+    </row>
+    <row r="1436" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1436" s="7"/>
+      <c r="B1436" s="8" t="s">
+        <v>3279</v>
+      </c>
+      <c r="C1436" s="7"/>
+      <c r="D1436" s="7"/>
+      <c r="E1436" s="8" t="s">
+        <v>3280</v>
+      </c>
+      <c r="F1436" s="7"/>
+      <c r="G1436" s="7"/>
+      <c r="H1436" s="8"/>
+      <c r="I1436" s="8"/>
+      <c r="J1436" s="8"/>
+    </row>
+    <row r="1437" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1437" s="7"/>
+      <c r="B1437" s="8" t="s">
+        <v>3281</v>
+      </c>
+      <c r="C1437" s="7"/>
+      <c r="D1437" s="7"/>
+      <c r="E1437" s="8" t="s">
+        <v>3282</v>
+      </c>
+      <c r="F1437" s="7"/>
+      <c r="G1437" s="7"/>
+      <c r="H1437" s="8"/>
+      <c r="I1437" s="8"/>
+      <c r="J1437" s="8"/>
+    </row>
+    <row r="1438" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1438" s="7"/>
+      <c r="B1438" s="8" t="s">
+        <v>3283</v>
+      </c>
+      <c r="C1438" s="7"/>
+      <c r="D1438" s="7"/>
+      <c r="E1438" s="8" t="s">
+        <v>3276</v>
+      </c>
+      <c r="F1438" s="7"/>
+      <c r="G1438" s="7"/>
+      <c r="H1438" s="8"/>
+      <c r="I1438" s="8"/>
+      <c r="J1438" s="8"/>
+    </row>
+    <row r="1439" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1439" s="7"/>
+      <c r="B1439" s="8" t="s">
+        <v>3284</v>
+      </c>
+      <c r="C1439" s="7"/>
+      <c r="D1439" s="7"/>
+      <c r="E1439" s="8" t="s">
+        <v>3259</v>
+      </c>
+      <c r="F1439" s="7"/>
+      <c r="G1439" s="7"/>
+      <c r="H1439" s="8"/>
+      <c r="I1439" s="8"/>
+      <c r="J1439" s="8"/>
+    </row>
+    <row r="1440" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1440" s="7"/>
+      <c r="B1440" s="8" t="s">
+        <v>3285</v>
+      </c>
+      <c r="C1440" s="7"/>
+      <c r="D1440" s="7"/>
+      <c r="E1440" s="8" t="s">
+        <v>3259</v>
+      </c>
+      <c r="F1440" s="7"/>
+      <c r="G1440" s="7"/>
+      <c r="H1440" s="8"/>
+      <c r="I1440" s="8"/>
+      <c r="J1440" s="8"/>
+    </row>
+    <row r="1441" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1441" s="7"/>
+      <c r="B1441" s="8" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1441" s="7"/>
+      <c r="D1441" s="7"/>
+      <c r="E1441" s="8" t="s">
+        <v>3287</v>
+      </c>
+      <c r="F1441" s="7"/>
+      <c r="G1441" s="7"/>
+      <c r="H1441" s="8"/>
+      <c r="I1441" s="8" t="s">
+        <v>3288</v>
+      </c>
+      <c r="J1441" s="8"/>
+    </row>
+    <row r="1442" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1442" s="7"/>
+      <c r="B1442" s="8" t="s">
+        <v>3289</v>
+      </c>
+      <c r="C1442" s="7"/>
+      <c r="D1442" s="7"/>
+      <c r="E1442" s="8" t="s">
+        <v>3290</v>
+      </c>
+      <c r="F1442" s="7"/>
+      <c r="G1442" s="7"/>
+      <c r="H1442" s="8"/>
+      <c r="I1442" s="8" t="s">
+        <v>3140</v>
+      </c>
+      <c r="J1442" s="8"/>
+    </row>
+    <row r="1443" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1443" s="7"/>
+      <c r="B1443" s="8" t="s">
+        <v>3291</v>
+      </c>
+      <c r="C1443" s="7"/>
+      <c r="D1443" s="7"/>
+      <c r="E1443" s="8" t="s">
+        <v>3292</v>
+      </c>
+      <c r="F1443" s="7"/>
+      <c r="G1443" s="7"/>
+      <c r="H1443" s="8"/>
+      <c r="I1443" s="8" t="s">
+        <v>3293</v>
+      </c>
+      <c r="J1443" s="8"/>
+    </row>
+    <row r="1444" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1444" s="7"/>
+      <c r="B1444" s="8" t="s">
+        <v>3294</v>
+      </c>
+      <c r="C1444" s="7"/>
+      <c r="D1444" s="7"/>
+      <c r="E1444" s="8" t="s">
+        <v>3295</v>
+      </c>
+      <c r="F1444" s="7"/>
+      <c r="G1444" s="7"/>
+      <c r="H1444" s="8"/>
+      <c r="I1444" s="8"/>
+      <c r="J1444" s="8"/>
+    </row>
+    <row r="1445" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1445" s="7"/>
+      <c r="B1445" s="8" t="s">
+        <v>3296</v>
+      </c>
+      <c r="C1445" s="7"/>
+      <c r="D1445" s="7"/>
+      <c r="E1445" s="8" t="s">
+        <v>3297</v>
+      </c>
+      <c r="F1445" s="7"/>
+      <c r="G1445" s="7"/>
+      <c r="H1445" s="8"/>
+      <c r="I1445" s="8"/>
+      <c r="J1445" s="8"/>
+    </row>
+    <row r="1446" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1446" s="7"/>
+      <c r="B1446" s="8" t="s">
+        <v>3298</v>
+      </c>
+      <c r="C1446" s="7"/>
+      <c r="D1446" s="7"/>
+      <c r="E1446" s="8" t="s">
+        <v>3299</v>
+      </c>
+      <c r="F1446" s="7"/>
+      <c r="G1446" s="7"/>
+      <c r="H1446" s="8"/>
+      <c r="I1446" s="8"/>
+      <c r="J1446" s="8"/>
+    </row>
+    <row r="1447" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1447" s="7"/>
+      <c r="B1447" s="8" t="s">
+        <v>3300</v>
+      </c>
+      <c r="C1447" s="7"/>
+      <c r="D1447" s="7"/>
+      <c r="E1447" s="8" t="s">
+        <v>3301</v>
+      </c>
+      <c r="F1447" s="7"/>
+      <c r="G1447" s="7"/>
+      <c r="H1447" s="8"/>
+      <c r="I1447" s="8"/>
+      <c r="J1447" s="8"/>
+    </row>
+    <row r="1448" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1448" s="7"/>
+      <c r="B1448" s="8" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1448" s="7"/>
+      <c r="D1448" s="7"/>
+      <c r="E1448" s="8" t="s">
+        <v>3303</v>
+      </c>
+      <c r="F1448" s="7"/>
+      <c r="G1448" s="7"/>
+      <c r="H1448" s="8"/>
+      <c r="I1448" s="8"/>
+      <c r="J1448" s="8"/>
+    </row>
+    <row r="1449" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1449" s="7"/>
+      <c r="B1449" s="8"/>
+      <c r="C1449" s="7"/>
+      <c r="D1449" s="7"/>
+      <c r="E1449" s="8"/>
+      <c r="F1449" s="7"/>
+      <c r="G1449" s="7"/>
+      <c r="H1449" s="8"/>
+      <c r="I1449" s="8"/>
+      <c r="J1449" s="8"/>
+    </row>
+    <row r="1450" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1450" s="7"/>
+      <c r="B1450" s="8"/>
+      <c r="C1450" s="7"/>
+      <c r="D1450" s="7"/>
+      <c r="E1450" s="8"/>
+      <c r="F1450" s="7"/>
+      <c r="G1450" s="7"/>
+      <c r="H1450" s="8"/>
+      <c r="I1450" s="8"/>
+      <c r="J1450" s="8"/>
+    </row>
+    <row r="1451" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1451" s="7"/>
+      <c r="B1451" s="8"/>
+      <c r="C1451" s="7"/>
+      <c r="D1451" s="7"/>
+      <c r="E1451" s="8"/>
+      <c r="F1451" s="7"/>
+      <c r="G1451" s="7"/>
+      <c r="H1451" s="8"/>
+      <c r="I1451" s="8"/>
+      <c r="J1451" s="8"/>
+    </row>
+    <row r="1452" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1452" s="7"/>
+      <c r="B1452" s="8"/>
+      <c r="C1452" s="7"/>
+      <c r="D1452" s="7"/>
+      <c r="E1452" s="8"/>
+      <c r="F1452" s="7"/>
+      <c r="G1452" s="7"/>
+      <c r="H1452" s="8"/>
+      <c r="I1452" s="8"/>
+      <c r="J1452" s="8"/>
+    </row>
+    <row r="1453" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1453" s="7">
+        <v>28</v>
+      </c>
+      <c r="B1453" s="8" t="s">
+        <v>3304</v>
+      </c>
+      <c r="C1453" s="7"/>
+      <c r="D1453" s="7">
+        <v>1762</v>
+      </c>
+      <c r="E1453" s="10" t="s">
+        <v>3305</v>
+      </c>
+      <c r="F1453" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1453" s="7"/>
+      <c r="H1453" s="10" t="s">
+        <v>3307</v>
+      </c>
+      <c r="I1453" s="10" t="s">
+        <v>3308</v>
+      </c>
+      <c r="J1453" s="8" t="s">
+        <v>3309</v>
+      </c>
+    </row>
+    <row r="1454" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1454" s="7">
+        <v>28</v>
+      </c>
+      <c r="B1454" s="8" t="s">
+        <v>3310</v>
+      </c>
+      <c r="C1454" s="7"/>
+      <c r="D1454" s="7">
+        <v>1780</v>
+      </c>
+      <c r="E1454" s="10" t="s">
+        <v>3311</v>
+      </c>
+      <c r="F1454" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1454" s="7"/>
+      <c r="H1454" s="10" t="s">
+        <v>3312</v>
+      </c>
+      <c r="I1454" s="10" t="s">
+        <v>3313</v>
+      </c>
+      <c r="J1454" s="8" t="s">
+        <v>3314</v>
+      </c>
+    </row>
+    <row r="1455" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1455" s="7">
+        <v>28</v>
+      </c>
+      <c r="B1455" s="8" t="s">
+        <v>3315</v>
+      </c>
+      <c r="C1455" s="7"/>
+      <c r="D1455" s="7">
+        <v>1782</v>
+      </c>
+      <c r="E1455" s="10" t="s">
+        <v>3316</v>
+      </c>
+      <c r="F1455" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1455" s="7"/>
+      <c r="H1455" s="10" t="s">
+        <v>3317</v>
+      </c>
+      <c r="I1455" s="10" t="s">
+        <v>3318</v>
+      </c>
+      <c r="J1455" s="8" t="s">
+        <v>3319</v>
+      </c>
+    </row>
+    <row r="1456" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1456" s="7">
+        <v>28</v>
+      </c>
+      <c r="B1456" s="8" t="s">
+        <v>3320</v>
+      </c>
+      <c r="C1456" s="7"/>
+      <c r="D1456" s="7">
+        <v>1783</v>
+      </c>
+      <c r="E1456" s="10" t="s">
+        <v>3321</v>
+      </c>
+      <c r="F1456" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1456" s="7"/>
+      <c r="H1456" s="10" t="s">
+        <v>3322</v>
+      </c>
+      <c r="I1456" s="10" t="s">
+        <v>3323</v>
+      </c>
+      <c r="J1456" s="8" t="s">
+        <v>3324</v>
+      </c>
+    </row>
+    <row r="1457" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1457" s="7">
+        <v>28</v>
+      </c>
+      <c r="B1457" s="8" t="s">
+        <v>3325</v>
+      </c>
+      <c r="C1457" s="7"/>
+      <c r="D1457" s="7">
+        <v>1791</v>
+      </c>
+      <c r="E1457" s="10" t="s">
+        <v>3326</v>
+      </c>
+      <c r="F1457" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1457" s="7"/>
+      <c r="H1457" s="10" t="s">
+        <v>3327</v>
+      </c>
+      <c r="I1457" s="10" t="s">
+        <v>3328</v>
+      </c>
+      <c r="J1457" s="8" t="s">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="1458" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1458" s="7">
+        <v>28</v>
+      </c>
+      <c r="B1458" s="8" t="s">
+        <v>3330</v>
+      </c>
+      <c r="C1458" s="7"/>
+      <c r="D1458" s="7">
+        <v>1766</v>
+      </c>
+      <c r="E1458" s="10" t="s">
+        <v>3331</v>
+      </c>
+      <c r="F1458" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1458" s="7"/>
+      <c r="H1458" s="10" t="s">
+        <v>3332</v>
+      </c>
+      <c r="I1458" s="10" t="s">
+        <v>3333</v>
+      </c>
+      <c r="J1458" s="8"/>
+    </row>
+    <row r="1459" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1459" s="7">
+        <v>28</v>
+      </c>
+      <c r="B1459" s="8" t="s">
+        <v>3334</v>
+      </c>
+      <c r="C1459" s="7"/>
+      <c r="D1459" s="7">
+        <v>1768</v>
+      </c>
+      <c r="E1459" s="10" t="s">
+        <v>3335</v>
+      </c>
+      <c r="F1459" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1459" s="7"/>
+      <c r="H1459" s="10" t="s">
+        <v>3312</v>
+      </c>
+      <c r="I1459" s="10" t="s">
+        <v>3336</v>
+      </c>
+      <c r="J1459" s="8" t="s">
+        <v>3337</v>
+      </c>
+    </row>
+    <row r="1460" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1460" s="7">
+        <v>28</v>
+      </c>
+      <c r="B1460" s="8" t="s">
+        <v>3338</v>
+      </c>
+      <c r="C1460" s="7"/>
+      <c r="D1460" s="7">
+        <v>1769</v>
+      </c>
+      <c r="E1460" s="10" t="s">
+        <v>3339</v>
+      </c>
+      <c r="F1460" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1460" s="7"/>
+      <c r="H1460" s="10" t="s">
+        <v>3312</v>
+      </c>
+      <c r="I1460" s="10" t="s">
+        <v>3340</v>
+      </c>
+      <c r="J1460" s="8" t="s">
+        <v>3337</v>
+      </c>
+    </row>
+    <row r="1461" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1461" s="7">
+        <v>28</v>
+      </c>
+      <c r="B1461" s="8" t="s">
+        <v>3341</v>
+      </c>
+      <c r="C1461" s="7"/>
+      <c r="D1461" s="7">
+        <v>1773</v>
+      </c>
+      <c r="E1461" s="10" t="s">
+        <v>3342</v>
+      </c>
+      <c r="F1461" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1461" s="7"/>
+      <c r="H1461" s="10" t="s">
+        <v>3343</v>
+      </c>
+      <c r="I1461" s="10" t="s">
+        <v>3344</v>
+      </c>
+      <c r="J1461" s="8" t="s">
+        <v>3345</v>
+      </c>
+    </row>
+    <row r="1462" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1462" s="7">
+        <v>28</v>
+      </c>
+      <c r="B1462" s="8" t="s">
+        <v>3346</v>
+      </c>
+      <c r="C1462" s="7"/>
+      <c r="D1462" s="7">
+        <v>1775</v>
+      </c>
+      <c r="E1462" s="10" t="s">
+        <v>3347</v>
+      </c>
+      <c r="F1462" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1462" s="7"/>
+      <c r="H1462" s="10" t="s">
+        <v>3312</v>
+      </c>
+      <c r="I1462" s="10" t="s">
+        <v>3348</v>
+      </c>
+      <c r="J1462" s="8" t="s">
+        <v>3349</v>
+      </c>
+    </row>
+    <row r="1463" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1463" s="7">
+        <v>28</v>
+      </c>
+      <c r="B1463" s="8" t="s">
+        <v>3350</v>
+      </c>
+      <c r="C1463" s="7"/>
+      <c r="D1463" s="7">
+        <v>1777</v>
+      </c>
+      <c r="E1463" s="10" t="s">
+        <v>3351</v>
+      </c>
+      <c r="F1463" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1463" s="7"/>
+      <c r="H1463" s="10" t="s">
+        <v>3312</v>
+      </c>
+      <c r="I1463" s="10" t="s">
+        <v>3352</v>
+      </c>
+      <c r="J1463" s="8" t="s">
+        <v>3353</v>
+      </c>
+    </row>
+    <row r="1464" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1464" s="7">
+        <v>28</v>
+      </c>
+      <c r="B1464" s="8" t="s">
+        <v>3354</v>
+      </c>
+      <c r="C1464" s="7"/>
+      <c r="D1464" s="7" t="s">
+        <v>3355</v>
+      </c>
+      <c r="E1464" s="10" t="s">
+        <v>3356</v>
+      </c>
+      <c r="F1464" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1464" s="7"/>
+      <c r="H1464" s="10" t="s">
+        <v>3312</v>
+      </c>
+      <c r="I1464" s="10" t="s">
+        <v>3357</v>
+      </c>
+      <c r="J1464" s="8" t="s">
+        <v>3358</v>
+      </c>
+    </row>
+    <row r="1465" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1465" s="7">
+        <v>28</v>
+      </c>
+      <c r="B1465" s="8" t="s">
+        <v>3359</v>
+      </c>
+      <c r="C1465" s="7"/>
+      <c r="D1465" s="7">
+        <v>1779</v>
+      </c>
+      <c r="E1465" s="10" t="s">
+        <v>3360</v>
+      </c>
+      <c r="F1465" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1465" s="7"/>
+      <c r="H1465" s="10" t="s">
+        <v>3361</v>
+      </c>
+      <c r="I1465" s="10" t="s">
+        <v>3362</v>
+      </c>
+      <c r="J1465" s="8" t="s">
+        <v>3363</v>
+      </c>
+    </row>
+    <row r="1466" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1466" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1466" s="8" t="s">
+        <v>3364</v>
+      </c>
+      <c r="C1466" s="7"/>
+      <c r="D1466" s="7" t="s">
+        <v>3365</v>
+      </c>
+      <c r="E1466" s="8" t="s">
+        <v>3366</v>
+      </c>
+      <c r="F1466" s="7" t="s">
+        <v>3367</v>
+      </c>
+      <c r="G1466" s="7"/>
+      <c r="H1466" s="8" t="s">
+        <v>3368</v>
+      </c>
+      <c r="I1466" s="8" t="s">
+        <v>3369</v>
+      </c>
+      <c r="J1466" s="10"/>
+    </row>
+    <row r="1467" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1467" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1467" s="8" t="s">
+        <v>3370</v>
+      </c>
+      <c r="C1467" s="7"/>
+      <c r="D1467" s="7" t="s">
+        <v>3371</v>
+      </c>
+      <c r="E1467" s="10" t="s">
+        <v>3372</v>
+      </c>
+      <c r="F1467" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1467" s="7"/>
+      <c r="H1467" s="8"/>
+      <c r="I1467" s="8"/>
+      <c r="J1467" s="10" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="1468" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1468" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1468" s="8" t="s">
+        <v>3373</v>
+      </c>
+      <c r="C1468" s="7"/>
+      <c r="D1468" s="7">
+        <v>1768</v>
+      </c>
+      <c r="E1468" s="10" t="s">
+        <v>3374</v>
+      </c>
+      <c r="F1468" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1468" s="7"/>
+      <c r="H1468" s="8"/>
+      <c r="I1468" s="8"/>
+      <c r="J1468" s="10" t="s">
+        <v>3375</v>
+      </c>
+    </row>
+    <row r="1469" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1469" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1469" s="8" t="s">
+        <v>3376</v>
+      </c>
+      <c r="C1469" s="7"/>
+      <c r="D1469" s="7">
+        <v>1783</v>
+      </c>
+      <c r="E1469" s="10" t="s">
+        <v>3377</v>
+      </c>
+      <c r="F1469" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1469" s="7"/>
+      <c r="H1469" s="8"/>
+      <c r="I1469" s="8"/>
+      <c r="J1469" s="10" t="s">
+        <v>3378</v>
+      </c>
+    </row>
+    <row r="1470" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1470" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1470" s="8" t="s">
+        <v>3379</v>
+      </c>
+      <c r="C1470" s="7"/>
+      <c r="D1470" s="7" t="s">
+        <v>3380</v>
+      </c>
+      <c r="E1470" s="10" t="s">
+        <v>3381</v>
+      </c>
+      <c r="F1470" s="7" t="s">
+        <v>3367</v>
+      </c>
+      <c r="G1470" s="7"/>
+      <c r="H1470" s="10" t="s">
+        <v>3382</v>
+      </c>
+      <c r="I1470" s="8"/>
+      <c r="J1470" s="10" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="1471" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1471" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1471" s="8" t="s">
+        <v>3383</v>
+      </c>
+      <c r="C1471" s="7"/>
+      <c r="D1471" s="7">
+        <v>1773</v>
+      </c>
+      <c r="E1471" s="10" t="s">
+        <v>3384</v>
+      </c>
+      <c r="F1471" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1471" s="7"/>
+      <c r="H1471" s="8"/>
+      <c r="I1471" s="10" t="s">
+        <v>3385</v>
+      </c>
+      <c r="J1471" s="10" t="s">
+        <v>3386</v>
+      </c>
+    </row>
+    <row r="1472" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1472" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1472" s="8" t="s">
+        <v>3387</v>
+      </c>
+      <c r="C1472" s="7"/>
+      <c r="D1472" s="7">
+        <v>1773</v>
+      </c>
+      <c r="E1472" s="10" t="s">
+        <v>3388</v>
+      </c>
+      <c r="F1472" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1472" s="7"/>
+      <c r="H1472" s="8"/>
+      <c r="I1472" s="10" t="s">
+        <v>3389</v>
+      </c>
+      <c r="J1472" s="10" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="1473" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1473" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1473" s="8" t="s">
+        <v>3390</v>
+      </c>
+      <c r="C1473" s="7"/>
+      <c r="D1473" s="7">
+        <v>1773</v>
+      </c>
+      <c r="E1473" s="10" t="s">
+        <v>3391</v>
+      </c>
+      <c r="F1473" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1473" s="7"/>
+      <c r="H1473" s="8"/>
+      <c r="I1473" s="10" t="s">
+        <v>3392</v>
+      </c>
+      <c r="J1473" s="10" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="1474" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1474" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1474" s="8" t="s">
+        <v>3393</v>
+      </c>
+      <c r="C1474" s="7"/>
+      <c r="D1474" s="7">
+        <v>1776</v>
+      </c>
+      <c r="E1474" s="10" t="s">
+        <v>3394</v>
+      </c>
+      <c r="F1474" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1474" s="7"/>
+      <c r="H1474" s="8"/>
+      <c r="I1474" s="10" t="s">
+        <v>3395</v>
+      </c>
+      <c r="J1474" s="10" t="s">
+        <v>3396</v>
+      </c>
+    </row>
+    <row r="1475" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1475" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1475" s="8" t="s">
+        <v>3397</v>
+      </c>
+      <c r="C1475" s="7"/>
+      <c r="D1475" s="7"/>
+      <c r="E1475" s="10" t="s">
+        <v>3398</v>
+      </c>
+      <c r="F1475" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1475" s="7"/>
+      <c r="H1475" s="8"/>
+      <c r="I1475" s="8" t="s">
+        <v>3399</v>
+      </c>
+      <c r="J1475" s="10" t="s">
+        <v>3400</v>
+      </c>
+    </row>
+    <row r="1476" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1476" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1476" s="8" t="s">
+        <v>3401</v>
+      </c>
+      <c r="C1476" s="7"/>
+      <c r="D1476" s="7">
+        <v>1777</v>
+      </c>
+      <c r="E1476" s="10" t="s">
+        <v>3402</v>
+      </c>
+      <c r="F1476" s="7" t="s">
+        <v>3306</v>
+      </c>
+      <c r="G1476" s="7"/>
+      <c r="H1476" s="8"/>
+      <c r="I1476" s="8"/>
+      <c r="J1476" s="10" t="s">
+        <v>3403</v>
+      </c>
+    </row>
+    <row r="1477" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1477" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1477" s="8" t="s">
+        <v>3404</v>
+      </c>
+      <c r="C1477" s="7"/>
+      <c r="D1477" s="7">
+        <v>1751</v>
+      </c>
+      <c r="E1477" s="10" t="s">
+        <v>3405</v>
+      </c>
+      <c r="F1477" s="7" t="s">
+        <v>3367</v>
+      </c>
+      <c r="G1477" s="7"/>
+      <c r="H1477" s="8"/>
+      <c r="I1477" s="8"/>
+      <c r="J1477" s="10" t="s">
+        <v>3406</v>
+      </c>
+    </row>
+    <row r="1478" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1478" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1478" s="8" t="s">
+        <v>3407</v>
+      </c>
+      <c r="C1478" s="7"/>
+      <c r="D1478" s="7">
+        <v>1758</v>
+      </c>
+      <c r="E1478" s="10" t="s">
+        <v>3408</v>
+      </c>
+      <c r="F1478" s="7" t="s">
+        <v>3367</v>
+      </c>
+      <c r="G1478" s="7"/>
+      <c r="H1478" s="8"/>
+      <c r="I1478" s="8"/>
+      <c r="J1478" s="10" t="s">
+        <v>3406</v>
+      </c>
+    </row>
+    <row r="1479" s="3" customFormat="1" customHeight="1" spans="1:10">
+      <c r="A1479" s="7">
+        <v>29</v>
+      </c>
+      <c r="B1479" s="8" t="s">
+        <v>3409</v>
+      </c>
+      <c r="C1479" s="7"/>
+      <c r="D1479" s="7">
+        <v>1777</v>
+      </c>
+      <c r="E1479" s="10" t="s">
+        <v>3384</v>
+      </c>
+      <c r="F1479" s="7" t="s">
+        <v>3367</v>
+      </c>
+      <c r="G1479" s="7"/>
+      <c r="H1479" s="8"/>
+      <c r="I1479" s="8" t="s">
+        <v>3410</v>
+      </c>
+      <c r="J1479" s="10" t="s">
+        <v>3411</v>
+      </c>
+    </row>
+    <row r="1480" customHeight="1" spans="1:10">
+      <c r="A1480" s="7">
+        <v>30</v>
+      </c>
+      <c r="B1480" s="8" t="s">
+        <v>3412</v>
+      </c>
+      <c r="C1480" s="7"/>
+      <c r="D1480" s="7">
+        <v>1762</v>
+      </c>
+      <c r="E1480" s="8" t="s">
+        <v>3413</v>
+      </c>
+      <c r="F1480" s="7"/>
+      <c r="G1480" s="7"/>
+      <c r="H1480" s="8" t="s">
+        <v>3414</v>
+      </c>
+      <c r="I1480" s="8"/>
+      <c r="J1480" s="8" t="s">
+        <v>3415</v>
+      </c>
+    </row>
+    <row r="1481" customHeight="1" spans="1:10">
+      <c r="A1481" s="7">
+        <v>30</v>
+      </c>
+      <c r="B1481" s="8" t="s">
+        <v>3416</v>
+      </c>
+      <c r="C1481" s="7"/>
+      <c r="D1481" s="7">
+        <v>1774</v>
+      </c>
+      <c r="E1481" s="8" t="s">
+        <v>3417</v>
+      </c>
+      <c r="F1481" s="7"/>
+      <c r="G1481" s="7"/>
+      <c r="H1481" s="8"/>
+      <c r="I1481" s="8"/>
+      <c r="J1481" s="8" t="s">
+        <v>3418</v>
+      </c>
+    </row>
+    <row r="1482" customHeight="1" spans="1:10">
+      <c r="A1482" s="7">
+        <v>30</v>
+      </c>
+      <c r="B1482" s="8" t="s">
+        <v>3419</v>
+      </c>
+      <c r="C1482" s="7"/>
+      <c r="D1482" s="7"/>
+      <c r="E1482" s="10" t="s">
+        <v>3420</v>
+      </c>
+      <c r="F1482" s="7"/>
+      <c r="G1482" s="7"/>
+      <c r="H1482" s="8" t="s">
+        <v>3421</v>
+      </c>
+      <c r="I1482" s="8"/>
+      <c r="J1482" s="8" t="s">
+        <v>3422</v>
+      </c>
+    </row>
+    <row r="1483" customHeight="1" spans="1:10">
+      <c r="A1483" s="7">
+        <v>30</v>
+      </c>
+      <c r="B1483" s="8" t="s">
+        <v>3423</v>
+      </c>
+      <c r="C1483" s="7"/>
+      <c r="D1483" s="7">
+        <v>1793</v>
+      </c>
+      <c r="E1483" s="8" t="s">
+        <v>3424</v>
+      </c>
+      <c r="F1483" s="7" t="s">
+        <v>3425</v>
+      </c>
+      <c r="G1483" s="7"/>
+      <c r="H1483" s="8" t="s">
+        <v>3426</v>
+      </c>
+      <c r="I1483" s="8" t="s">
+        <v>3427</v>
+      </c>
+      <c r="J1483" s="8" t="s">
+        <v>3428</v>
+      </c>
+    </row>
+    <row r="1484" customHeight="1" spans="1:10">
+      <c r="A1484" s="7">
+        <v>30</v>
+      </c>
+      <c r="B1484" s="8" t="s">
+        <v>3429</v>
+      </c>
+      <c r="C1484" s="7"/>
+      <c r="D1484" s="7">
+        <v>1796</v>
+      </c>
+      <c r="E1484" s="8" t="s">
+        <v>3430</v>
+      </c>
+      <c r="F1484" s="7"/>
+      <c r="G1484" s="7"/>
+      <c r="H1484" s="8"/>
+      <c r="I1484" s="8"/>
+      <c r="J1484" s="8" t="s">
+        <v>3431</v>
+      </c>
+    </row>
+    <row r="1485" customHeight="1" spans="1:10">
+      <c r="A1485" s="7">
+        <v>30</v>
+      </c>
+      <c r="B1485" s="8" t="s">
+        <v>3432</v>
+      </c>
+      <c r="C1485" s="7"/>
+      <c r="D1485" s="7">
+        <v>1796</v>
+      </c>
+      <c r="E1485" s="8" t="s">
+        <v>3433</v>
+      </c>
+      <c r="F1485" s="7"/>
+      <c r="G1485" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H1485" s="8" t="s">
+        <v>3434</v>
+      </c>
+      <c r="I1485" s="8"/>
+      <c r="J1485" s="8" t="s">
+        <v>3435</v>
+      </c>
+    </row>
+    <row r="1486" customHeight="1" spans="1:10">
+      <c r="A1486" s="7">
+        <v>30</v>
+      </c>
+      <c r="B1486" s="8" t="s">
+        <v>3436</v>
+      </c>
+      <c r="C1486" s="7"/>
+      <c r="D1486" s="7">
+        <v>1796</v>
+      </c>
+      <c r="E1486" s="8" t="s">
+        <v>3437</v>
+      </c>
+      <c r="F1486" s="7" t="s">
+        <v>3438</v>
+      </c>
+      <c r="G1486" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H1486" s="9" t="s">
+        <v>3439</v>
+      </c>
+      <c r="I1486" s="8" t="s">
+        <v>3440</v>
+      </c>
+      <c r="J1486" s="8" t="s">
+        <v>3441</v>
+      </c>
+    </row>
+    <row r="1487" customHeight="1" spans="1:10">
+      <c r="A1487" s="7">
+        <v>30</v>
+      </c>
+      <c r="B1487" s="8" t="s">
+        <v>3442</v>
+      </c>
+      <c r="C1487" s="7"/>
+      <c r="D1487" s="7">
+        <v>1796</v>
+      </c>
+      <c r="E1487" s="8" t="s">
+        <v>3443</v>
+      </c>
+      <c r="F1487" s="7"/>
+      <c r="G1487" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1487" s="8" t="s">
+        <v>3444</v>
+      </c>
+      <c r="I1487" s="8"/>
+      <c r="J1487" s="8" t="s">
+        <v>3445</v>
+      </c>
+    </row>
+    <row r="1488" customHeight="1" spans="1:10">
+      <c r="A1488" s="7">
+        <v>30</v>
+      </c>
+      <c r="B1488" s="8" t="s">
+        <v>3446</v>
+      </c>
+      <c r="C1488" s="7"/>
+      <c r="D1488" s="7">
+        <v>1806</v>
+      </c>
+      <c r="E1488" s="10" t="s">
+        <v>3447</v>
+      </c>
+      <c r="F1488" s="7"/>
+      <c r="G1488" s="7"/>
+      <c r="H1488" s="8"/>
+      <c r="I1488" s="8"/>
+      <c r="J1488" s="10" t="s">
+        <v>3448</v>
+      </c>
+    </row>
+    <row r="1489" customHeight="1" spans="1:10">
+      <c r="A1489" s="7">
+        <v>30</v>
+      </c>
+      <c r="B1489" s="8" t="s">
+        <v>3449</v>
+      </c>
+      <c r="C1489" s="7"/>
+      <c r="D1489" s="7" t="s">
+        <v>3450</v>
+      </c>
+      <c r="E1489" s="10" t="s">
+        <v>3451</v>
+      </c>
+      <c r="F1489" s="7"/>
+      <c r="G1489" s="7"/>
+      <c r="H1489" s="8"/>
+      <c r="I1489" s="8"/>
+      <c r="J1489" s="10" t="s">
+        <v>3452</v>
+      </c>
+    </row>
+    <row r="1490" customHeight="1" spans="1:10">
+      <c r="A1490" s="7">
+        <v>30</v>
+      </c>
+      <c r="B1490" s="8" t="s">
+        <v>3453</v>
+      </c>
+      <c r="C1490" s="7"/>
+      <c r="D1490" s="7" t="s">
+        <v>3454</v>
+      </c>
+      <c r="E1490" s="10" t="s">
+        <v>3455</v>
+      </c>
+      <c r="F1490" s="7"/>
+      <c r="G1490" s="7"/>
+      <c r="H1490" s="8"/>
+      <c r="I1490" s="8"/>
+      <c r="J1490" s="10" t="s">
+        <v>3456</v>
+      </c>
+    </row>
+    <row r="1491" customHeight="1" spans="1:10">
+      <c r="A1491" s="7">
+        <v>30</v>
+      </c>
+      <c r="B1491" s="8" t="s">
+        <v>3457</v>
+      </c>
+      <c r="C1491" s="7"/>
+      <c r="D1491" s="7" t="s">
+        <v>3458</v>
+      </c>
+      <c r="E1491" s="10" t="s">
+        <v>3459</v>
+      </c>
+      <c r="F1491" s="7"/>
+      <c r="G1491" s="7"/>
+      <c r="H1491" s="8"/>
+      <c r="I1491" s="8"/>
+      <c r="J1491" s="10" t="s">
+        <v>3460</v>
+      </c>
+    </row>
+    <row r="1492" customHeight="1" spans="1:10">
+      <c r="A1492" s="7">
         <v>32</v>
       </c>
-      <c r="B1328" s="8" t="s">
-        <v>3152</v>
-      </c>
-      <c r="C1328" s="7"/>
-      <c r="D1328" s="7">
+      <c r="B1492" s="8" t="s">
+        <v>3461</v>
+      </c>
+      <c r="C1492" s="7"/>
+      <c r="D1492" s="7">
         <v>1789</v>
       </c>
-      <c r="E1328" s="8" t="s">
-        <v>3153</v>
-      </c>
-      <c r="F1328" s="7" t="s">
-        <v>3154</v>
-      </c>
-      <c r="G1328" s="7"/>
-      <c r="H1328" s="8" t="s">
-        <v>3155</v>
-      </c>
-      <c r="I1328" s="8" t="s">
-        <v>3156</v>
-      </c>
-      <c r="J1328" s="8" t="s">
-        <v>3157</v>
-      </c>
-    </row>
-    <row r="1329" customHeight="1" spans="1:10">
-      <c r="A1329" s="7">
+      <c r="E1492" s="8" t="s">
+        <v>3462</v>
+      </c>
+      <c r="F1492" s="7" t="s">
+        <v>3463</v>
+      </c>
+      <c r="G1492" s="7"/>
+      <c r="H1492" s="8" t="s">
+        <v>3464</v>
+      </c>
+      <c r="I1492" s="8" t="s">
+        <v>3465</v>
+      </c>
+      <c r="J1492" s="8" t="s">
+        <v>3466</v>
+      </c>
+    </row>
+    <row r="1493" customHeight="1" spans="1:10">
+      <c r="A1493" s="7">
         <v>32</v>
       </c>
-      <c r="B1329" s="8" t="s">
-        <v>3158</v>
-      </c>
-      <c r="C1329" s="7"/>
-      <c r="D1329" s="7">
+      <c r="B1493" s="8" t="s">
+        <v>3467</v>
+      </c>
+      <c r="C1493" s="7"/>
+      <c r="D1493" s="7">
         <v>1788</v>
       </c>
-      <c r="E1329" s="8" t="s">
-        <v>3159</v>
-      </c>
-      <c r="F1329" s="7" t="s">
-        <v>3154</v>
-      </c>
-      <c r="G1329" s="7"/>
-      <c r="H1329" s="8" t="s">
-        <v>3160</v>
-      </c>
-      <c r="I1329" s="8"/>
-      <c r="J1329" s="8" t="s">
-        <v>3161</v>
-      </c>
-    </row>
-    <row r="1330" customHeight="1" spans="1:10">
-      <c r="A1330" s="7">
+      <c r="E1493" s="8" t="s">
+        <v>3468</v>
+      </c>
+      <c r="F1493" s="7" t="s">
+        <v>3463</v>
+      </c>
+      <c r="G1493" s="7"/>
+      <c r="H1493" s="8" t="s">
+        <v>3469</v>
+      </c>
+      <c r="I1493" s="8"/>
+      <c r="J1493" s="8" t="s">
+        <v>3470</v>
+      </c>
+    </row>
+    <row r="1494" customHeight="1" spans="1:10">
+      <c r="A1494" s="7">
         <v>32</v>
       </c>
-      <c r="B1330" s="8" t="s">
-        <v>3162</v>
-      </c>
-      <c r="C1330" s="7"/>
-      <c r="D1330" s="7">
+      <c r="B1494" s="8" t="s">
+        <v>3471</v>
+      </c>
+      <c r="C1494" s="7"/>
+      <c r="D1494" s="7">
         <v>1790</v>
       </c>
-      <c r="E1330" s="8" t="s">
-        <v>3163</v>
-      </c>
-      <c r="F1330" s="7" t="s">
-        <v>3154</v>
-      </c>
-      <c r="G1330" s="7"/>
-      <c r="H1330" s="8" t="s">
-        <v>3164</v>
-      </c>
-      <c r="I1330" s="8" t="s">
-        <v>3156</v>
-      </c>
-      <c r="J1330" s="8" t="s">
-        <v>3165</v>
-      </c>
-    </row>
-    <row r="1331" customHeight="1" spans="1:10">
-      <c r="A1331" s="7">
+      <c r="E1494" s="8" t="s">
+        <v>3472</v>
+      </c>
+      <c r="F1494" s="7" t="s">
+        <v>3463</v>
+      </c>
+      <c r="G1494" s="7"/>
+      <c r="H1494" s="8" t="s">
+        <v>3473</v>
+      </c>
+      <c r="I1494" s="8" t="s">
+        <v>3465</v>
+      </c>
+      <c r="J1494" s="8" t="s">
+        <v>3474</v>
+      </c>
+    </row>
+    <row r="1495" customHeight="1" spans="1:10">
+      <c r="A1495" s="7">
         <v>32</v>
       </c>
-      <c r="B1331" s="8" t="s">
-        <v>3166</v>
-      </c>
-      <c r="C1331" s="7"/>
-      <c r="D1331" s="7">
+      <c r="B1495" s="8" t="s">
+        <v>3475</v>
+      </c>
+      <c r="C1495" s="7"/>
+      <c r="D1495" s="7">
         <v>1781</v>
       </c>
-      <c r="E1331" s="8" t="s">
-        <v>3167</v>
-      </c>
-      <c r="F1331" s="7" t="s">
-        <v>3154</v>
-      </c>
-      <c r="G1331" s="7"/>
-      <c r="H1331" s="8" t="s">
-        <v>3168</v>
-      </c>
-      <c r="I1331" s="8"/>
-      <c r="J1331" s="8" t="s">
-        <v>3165</v>
+      <c r="E1495" s="8" t="s">
+        <v>3476</v>
+      </c>
+      <c r="F1495" s="7" t="s">
+        <v>3463</v>
+      </c>
+      <c r="G1495" s="7"/>
+      <c r="H1495" s="8" t="s">
+        <v>3477</v>
+      </c>
+      <c r="I1495" s="8"/>
+      <c r="J1495" s="8" t="s">
+        <v>3474</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J1331" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:J1331">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J1495" etc:filterBottomFollowUsedRange="0">
+    <sortState ref="A2:J1495">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -48874,175 +52501,175 @@
   <sheetData>
     <row r="1" ht="14.55" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>3169</v>
+        <v>3478</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3170</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="2" ht="14.55" spans="1:2">
       <c r="A2" s="1" t="s">
-        <v>3171</v>
+        <v>3480</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3172</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="3" ht="14.55" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>3173</v>
+        <v>3482</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>3174</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="4" ht="14.55" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>3175</v>
+        <v>3484</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>3176</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="5" ht="14.55" spans="1:2">
       <c r="A5" s="1" t="s">
-        <v>3177</v>
+        <v>3486</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3178</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="6" ht="14.55" spans="1:2">
       <c r="A6" s="1" t="s">
-        <v>3179</v>
+        <v>3488</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>3180</v>
+        <v>3489</v>
       </c>
     </row>
     <row r="7" ht="14.55" spans="1:2">
       <c r="A7" s="1" t="s">
-        <v>3181</v>
+        <v>3490</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>3182</v>
+        <v>3491</v>
       </c>
     </row>
     <row r="8" ht="14.55" spans="1:2">
       <c r="A8" s="1" t="s">
-        <v>3183</v>
+        <v>3492</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>3184</v>
+        <v>3493</v>
       </c>
     </row>
     <row r="9" ht="14.55" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>3185</v>
+        <v>3494</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>3186</v>
+        <v>3495</v>
       </c>
     </row>
     <row r="10" ht="14.55" spans="1:2">
       <c r="A10" s="1" t="s">
-        <v>3187</v>
+        <v>3496</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>3188</v>
+        <v>3497</v>
       </c>
     </row>
     <row r="11" ht="14.55" spans="1:2">
       <c r="A11" s="1" t="s">
-        <v>3189</v>
+        <v>3498</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>3190</v>
+        <v>3499</v>
       </c>
     </row>
     <row r="12" ht="14.55" spans="1:2">
       <c r="A12" s="1" t="s">
-        <v>3191</v>
+        <v>3500</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>3192</v>
+        <v>3501</v>
       </c>
     </row>
     <row r="13" ht="14.55" spans="1:2">
       <c r="A13" s="1" t="s">
-        <v>3193</v>
+        <v>3502</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>3194</v>
+        <v>3503</v>
       </c>
     </row>
     <row r="14" ht="14.55" spans="1:2">
       <c r="A14" s="1" t="s">
-        <v>3195</v>
+        <v>3504</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>3196</v>
+        <v>3505</v>
       </c>
     </row>
     <row r="15" ht="14.55" spans="1:2">
       <c r="A15" s="1" t="s">
-        <v>3197</v>
+        <v>3506</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>3198</v>
+        <v>3507</v>
       </c>
     </row>
     <row r="16" ht="14.55" spans="1:2">
       <c r="A16" s="1" t="s">
-        <v>3199</v>
+        <v>3508</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>3200</v>
+        <v>3509</v>
       </c>
     </row>
     <row r="17" ht="14.55" spans="1:2">
       <c r="A17" s="1" t="s">
-        <v>3201</v>
+        <v>3510</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>3202</v>
+        <v>3511</v>
       </c>
     </row>
     <row r="18" ht="14.55" spans="1:2">
       <c r="A18" s="1" t="s">
-        <v>3203</v>
+        <v>3512</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>3204</v>
+        <v>3513</v>
       </c>
     </row>
     <row r="19" ht="14.55" spans="1:2">
       <c r="A19" s="1" t="s">
-        <v>3205</v>
+        <v>3514</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>3206</v>
+        <v>3515</v>
       </c>
     </row>
     <row r="20" ht="14.55" spans="1:2">
       <c r="A20" s="1" t="s">
-        <v>3207</v>
+        <v>3516</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>3208</v>
+        <v>3517</v>
       </c>
     </row>
     <row r="21" ht="14.55" spans="1:2">
       <c r="A21" s="1" t="s">
-        <v>3209</v>
+        <v>3518</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>3210</v>
+        <v>3519</v>
       </c>
     </row>
     <row r="22" ht="14.55" spans="1:2">
       <c r="A22" s="1" t="s">
-        <v>3211</v>
+        <v>3520</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>2726</v>
@@ -49050,31 +52677,31 @@
     </row>
     <row r="23" ht="14.55" spans="1:2">
       <c r="A23" s="1" t="s">
-        <v>3212</v>
+        <v>3521</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>3213</v>
+        <v>3522</v>
       </c>
     </row>
     <row r="24" ht="14.55" spans="1:2">
       <c r="A24" s="1" t="s">
-        <v>3214</v>
+        <v>3523</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>3215</v>
+        <v>3524</v>
       </c>
     </row>
     <row r="25" ht="14.55" spans="1:2">
       <c r="A25" s="1" t="s">
-        <v>3216</v>
+        <v>3525</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>3217</v>
+        <v>3526</v>
       </c>
     </row>
     <row r="26" ht="14.55" spans="1:2">
       <c r="A26" s="1" t="s">
-        <v>3218</v>
+        <v>3527</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>2986</v>
@@ -49082,130 +52709,130 @@
     </row>
     <row r="27" ht="14.55" spans="1:2">
       <c r="A27" s="1" t="s">
-        <v>3219</v>
+        <v>3528</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>3220</v>
+        <v>3529</v>
       </c>
     </row>
     <row r="28" ht="14.55" spans="1:2">
       <c r="A28" s="1" t="s">
-        <v>3221</v>
+        <v>3530</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>3222</v>
+        <v>3531</v>
       </c>
     </row>
     <row r="29" ht="14.55" spans="1:2">
       <c r="A29" s="1" t="s">
-        <v>3223</v>
+        <v>3532</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>3224</v>
+        <v>3533</v>
       </c>
     </row>
     <row r="30" ht="14.55" spans="1:2">
       <c r="A30" s="1" t="s">
-        <v>3225</v>
+        <v>3534</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>3226</v>
+        <v>3535</v>
       </c>
     </row>
     <row r="31" ht="14.55" spans="1:2">
       <c r="A31" s="1" t="s">
-        <v>3227</v>
+        <v>3536</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>3228</v>
+        <v>3537</v>
       </c>
     </row>
     <row r="32" ht="14.55" spans="1:2">
       <c r="A32" s="1" t="s">
-        <v>3229</v>
+        <v>3538</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>3230</v>
+        <v>3539</v>
       </c>
     </row>
     <row r="33" ht="14.55" spans="1:2">
       <c r="A33" s="1" t="s">
-        <v>3231</v>
+        <v>3540</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>3232</v>
+        <v>3541</v>
       </c>
     </row>
     <row r="34" ht="14.55" spans="1:2">
       <c r="A34" s="1" t="s">
-        <v>3233</v>
+        <v>3542</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>3234</v>
+        <v>3543</v>
       </c>
     </row>
     <row r="35" ht="14.55" spans="1:2">
       <c r="A35" s="1" t="s">
-        <v>3235</v>
+        <v>3544</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>3236</v>
+        <v>3545</v>
       </c>
     </row>
     <row r="36" ht="14.55" spans="1:2">
       <c r="A36" s="1" t="s">
-        <v>3237</v>
+        <v>3546</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>3238</v>
+        <v>3547</v>
       </c>
     </row>
     <row r="37" ht="14.55" spans="1:2">
       <c r="A37" s="1" t="s">
-        <v>3239</v>
+        <v>3548</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>3240</v>
+        <v>3549</v>
       </c>
     </row>
     <row r="38" ht="14.55" spans="1:2">
       <c r="A38" s="1" t="s">
-        <v>3241</v>
+        <v>3550</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>3242</v>
+        <v>3551</v>
       </c>
     </row>
     <row r="39" ht="14.55" spans="1:2">
       <c r="A39" s="1" t="s">
-        <v>3243</v>
+        <v>3552</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>3244</v>
+        <v>3553</v>
       </c>
     </row>
     <row r="40" ht="14.55" spans="1:2">
       <c r="A40" s="1" t="s">
-        <v>3245</v>
+        <v>3554</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>3246</v>
+        <v>3555</v>
       </c>
     </row>
     <row r="41" ht="14.55" spans="1:2">
       <c r="A41" s="1" t="s">
-        <v>3247</v>
+        <v>3556</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>3248</v>
+        <v>3557</v>
       </c>
     </row>
     <row r="42" ht="14.55" spans="1:2">
       <c r="A42" s="1" t="s">
-        <v>3249</v>
+        <v>3558</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>3250</v>
+        <v>3559</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/Hob.xlsx
+++ b/xlsx/Hob.xlsx
@@ -9,12 +9,11 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="21925" windowHeight="9582"/>
+    <workbookView windowWidth="21942" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Hob. " sheetId="2" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Hob. '!$A$1:$J$1680</definedName>
@@ -57396,7 +57395,7 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:J1680" etc:filterBottomFollowUsedRange="0">
-    <sortState ref="A2:J1680">
+    <sortState ref="A1:J1680">
       <sortCondition ref="A1"/>
     </sortState>
     <extLst/>
@@ -57404,7 +57403,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="F1:K1 D1 K2:K314" emptyCellReference="1"/>
+    <ignoredError sqref="K2:K314 D1 F1:K1" emptyCellReference="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -57759,15 +57758,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.61261261261261" defaultRowHeight="14.1"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>